--- a/profiles/rocphotos/profile-crate/ro-crate-metadata.xlsx
+++ b/profiles/rocphotos/profile-crate/ro-crate-metadata.xlsx
@@ -13,13 +13,14 @@
     <sheet sheetId="7" name="@type=rdfs_Class" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="@type=rdf_Property" state="visible" r:id="rId11"/>
     <sheet sheetId="9" name="@type=ItemList" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="@type=oa_Motivation" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="296">
   <si>
     <t>Name</t>
   </si>
@@ -759,7 +760,10 @@
     <t>"http://www.w3.org/ns/oa#motivatedBy"</t>
   </si>
   <si>
-    <t>Always oa:identifying — the annotation says who this is. Left range-unconstrained: the validator resolves a range reference within the target crate, and rocphotos does not (yet) describe oa:identifying as an entity of its own.</t>
+    <t>Always oa:identifying — the annotation says who this is. The value comes from an ItemList so more motivations can be added later. As with any ItemList value, the crate must carry the oa:identifying entity itself, matching the one in this profile.</t>
+  </si>
+  <si>
+    <t>"#itemlist_motivation"</t>
   </si>
   <si>
     <t>#prop_standoff_writtenToFile</t>
@@ -892,6 +896,18 @@
   </si>
   <si>
     <t>"http://www.w3.org/ns/oa#identifying"</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/ns/oa#identifying</t>
+  </si>
+  <si>
+    <t>oa:Motivation</t>
+  </si>
+  <si>
+    <t>identifying</t>
+  </si>
+  <si>
+    <t>The motivation for when the user intends to assign an identity to the Target or identify what is being depicted or described in the Target.</t>
   </si>
 </sst>
 </file>
@@ -1377,6 +1393,48 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="4" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B4"/>
@@ -3012,34 +3070,37 @@
       <c r="G40" t="s">
         <v>246</v>
       </c>
+      <c r="H40" t="s">
+        <v>247</v>
+      </c>
       <c r="I40">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B41" t="s">
         <v>111</v>
       </c>
       <c r="C41" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D41" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E41" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F41" t="s">
         <v>231</v>
       </c>
       <c r="G41" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H41" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I41">
         <v>1</v>
@@ -3047,7 +3108,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B42" t="s">
         <v>111</v>
@@ -3065,7 +3126,7 @@
         <v>242</v>
       </c>
       <c r="G42" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H42" t="s">
         <v>195</v>
@@ -3076,7 +3137,7 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B43" t="s">
         <v>111</v>
@@ -3094,7 +3155,7 @@
         <v>158</v>
       </c>
       <c r="G43" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H43" t="s">
         <v>115</v>
@@ -3105,25 +3166,25 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B44" t="s">
         <v>111</v>
       </c>
       <c r="C44" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D44" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E44" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F44" t="s">
         <v>158</v>
       </c>
       <c r="G44" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H44" t="s">
         <v>115</v>
@@ -3134,7 +3195,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B45" t="s">
         <v>111</v>
@@ -3149,10 +3210,10 @@
         <v>112</v>
       </c>
       <c r="F45" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G45" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H45" t="s">
         <v>115</v>
@@ -3163,7 +3224,7 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B46" t="s">
         <v>111</v>
@@ -3178,10 +3239,10 @@
         <v>161</v>
       </c>
       <c r="F46" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H46" t="s">
         <v>192</v>
@@ -3189,25 +3250,25 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B47" t="s">
         <v>111</v>
       </c>
       <c r="C47" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D47" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E47" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F47" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G47" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H47" t="s">
         <v>115</v>
@@ -3218,25 +3279,25 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B48" t="s">
         <v>111</v>
       </c>
       <c r="C48" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D48" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E48" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F48" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G48" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H48" t="s">
         <v>115</v>
@@ -3244,25 +3305,25 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B49" t="s">
         <v>111</v>
       </c>
       <c r="C49" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D49" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E49" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F49" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G49" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H49" t="s">
         <v>153</v>
@@ -3273,25 +3334,25 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B50" t="s">
         <v>111</v>
       </c>
       <c r="C50" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D50" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E50" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F50" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G50" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H50" t="s">
         <v>115</v>
@@ -3302,25 +3363,25 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B51" t="s">
         <v>111</v>
       </c>
       <c r="C51" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D51" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E51" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F51" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G51" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H51" t="s">
         <v>115</v>
@@ -3357,24 +3418,24 @@
         <v>8</v>
       </c>
       <c r="E1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>

--- a/profiles/rocphotos/profile-crate/ro-crate-metadata.xlsx
+++ b/profiles/rocphotos/profile-crate/ro-crate-metadata.xlsx
@@ -12,15 +12,16 @@
     <sheet sheetId="6" name="@type=ResourceDescriptor" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="@type=rdfs_Class" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="@type=rdf_Property" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="@type=ItemList" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="@type=oa_Motivation" state="visible" r:id="rId13"/>
+    <sheet sheetId="9" name="@type=PropertyValue" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="@type=ItemList" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="@type=oa_Motivation" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="414">
   <si>
     <t>Name</t>
   </si>
@@ -43,7 +44,7 @@
     <t>name</t>
   </si>
   <si>
-    <t>rocphotos Profile</t>
+    <t>RO-Crate Photo Collection Profile</t>
   </si>
   <si>
     <t>description</t>
@@ -73,7 +74,7 @@
     <t>license</t>
   </si>
   <si>
-    <t>GPL-3.0</t>
+    <t>CCBY4</t>
   </si>
   <si>
     <t>author</t>
@@ -106,6 +107,9 @@
     <t>https://w3id.org/ldac/rocphotos/terms#</t>
   </si>
   <si>
+    <t>isPartOf</t>
+  </si>
+  <si>
     <t>profile-documentation.md</t>
   </si>
   <si>
@@ -115,6 +119,9 @@
     <t>Profile documentation</t>
   </si>
   <si>
+    <t>"https://w3id.org/ldac/rocphotos/profile"</t>
+  </si>
+  <si>
     <t>#author</t>
   </si>
   <si>
@@ -154,7 +161,7 @@
     <t>"http://www.w3.org/ns/dx/prof/role/schema"</t>
   </si>
   <si>
-    <t>["#Root_Data_Entity", "#prop_root_name", "#prop_root_hasPart", "#prop_root_mentions", "#class_SubCollection", "#prop_subcollection_name", "#class_Photo", "#prop_photo_name", "#prop_photo_title", "#prop_photo_description", "#prop_photo_dateCreated", "#prop_photo_dateModified", "#prop_photo_keywords", "#prop_photo_rating", "#prop_photo_exifData", "#prop_photo_about", "#prop_photo_regions", "#prop_photo_thumbnail", "#prop_photo_processingError", "#class_Thumbnail", "#prop_thumbnail_name", "#class_AlbumItem", "#prop_albumitem_specializationOf", "#class_Album", "#prop_album_name", "#prop_album_description", "#prop_album_hasPart", "#MainPersonClass", "#prop_person_name", "#InstancePersonClass", "#prop_personinstance_name", "#prop_personinstance_specializationOf", "#MainPetClass", "#prop_pet_name", "#InstancePetClass", "#prop_petinstance_name", "#prop_petinstance_specializationOf", "#class_ImageRegion_Exif", "#prop_region_name", "#prop_region_regionType", "#prop_region_about", "#prop_region_xPosition", "#prop_region_yPosition", "#prop_region_width", "#prop_region_height", "#class_ImageRegion_Standoff", "#prop_standoff_name", "#prop_standoff_regionType", "#prop_standoff_hasTarget", "#prop_standoff_hasBody", "#prop_standoff_motivatedBy", "#prop_standoff_writtenToFile", "#class_RegionBody", "#prop_regionbody_specializationOf", "#class_ExifValue", "#prop_exif_name", "#prop_exif_value", "#class_FaceEmbedding", "#prop_embedding_name", "#prop_embedding_about", "#prop_embedding_sourceImage", "#prop_embedding_sourceRegion", "#prop_embedding_embedding", "#prop_embedding_model", "#prop_embedding_modelVersion", "#itemlist_motivation"]</t>
+    <t>["#RO-Crate_Metadata_Descriptor", "#RO-Crate_Metadata_Descriptor.id", "#RO-Crate_Metadata_Descriptor.about", "#propertyValue_RO-Crate_Metadata_Descriptor.id", "#class_MainCollectionRoot", "#prop_mainroot_name", "#prop_mainroot_hasPart", "#class_FolderCollectionRoot", "#prop_folderroot_name", "#prop_folderroot_hasPart", "#class_FacesRoot", "#prop_facesroot_name", "#prop_facesroot_hasPart", "#class_SubCollection", "#prop_subcollection_name", "#class_Photo", "#prop_photo_name", "#prop_photo_title", "#prop_photo_description", "#prop_photo_dateCreated", "#prop_photo_dateModified", "#prop_photo_keywords", "#prop_photo_rating", "#prop_photo_exifData", "#prop_photo_about", "#prop_photo_regions", "#prop_photo_thumbnail", "#prop_photo_processingError", "#class_Thumbnail", "#prop_thumbnail_name", "#class_AlbumItem", "#prop_albumitem_specializationOf", "#class_Album", "#prop_album_name", "#prop_album_description", "#prop_album_hasPart", "#MainPersonClass", "#prop_person_name", "#InstancePersonClass", "#prop_personinstance_name", "#prop_personinstance_specializationOf", "#MainPetClass", "#prop_pet_name", "#InstancePetClass", "#prop_petinstance_name", "#prop_petinstance_specializationOf", "#class_ImageRegion_Exif", "#prop_region_name", "#prop_region_regionType", "#prop_region_about", "#prop_region_xPosition", "#prop_region_yPosition", "#prop_region_width", "#prop_region_height", "#class_ImageRegion_Standoff", "#prop_standoff_name", "#prop_standoff_regionType", "#prop_standoff_hasTarget", "#prop_standoff_hasBody", "#prop_standoff_motivatedBy", "#prop_standoff_writtenToFile", "#class_RegionBody", "#prop_regionbody_specializationOf", "#class_ExifValue", "#prop_exif_name", "#prop_exif_value", "#class_FaceEmbedding", "#prop_embedding_name", "#prop_embedding_about", "#prop_embedding_sourceImage", "#prop_embedding_sourceRegion", "#prop_embedding_embedding", "#prop_embedding_model", "#prop_embedding_modelVersion", "#itemlist_motivation", "#prop_person_description", "#prop_person_birthDate", "#prop_region_nameInFile", "#SpouseRelationshipClass", "#ParentChildRelationshipClass", "#prop_spouse_connects", "#prop_parentchild_source", "#prop_parentchild_target", "#prop_spouse_beginningDate", "#prop_spouse_endDate", "#prop_parentchild_beginningDate", "#prop_parentchild_endDate"]</t>
   </si>
   <si>
     <t>#hasGuidance</t>
@@ -166,28 +173,73 @@
     <t>"http://www.w3.org/ns/dx/prof/role/guidance"</t>
   </si>
   <si>
+    <t>rdfs:label</t>
+  </si>
+  <si>
     <t>prov:specializationOf</t>
   </si>
   <si>
+    <t>rdfs:comment</t>
+  </si>
+  <si>
     <t>sh:minCount</t>
   </si>
   <si>
     <t>sh:maxCount</t>
   </si>
   <si>
-    <t>#Root_Data_Entity</t>
+    <t>#RO-Crate_Metadata_Descriptor</t>
   </si>
   <si>
     <t>rdfs:Class</t>
   </si>
   <si>
-    <t>Root Data Entity</t>
+    <t>RO-Crate Metadata Descriptor</t>
+  </si>
+  <si>
+    <t>CreativeWork</t>
+  </si>
+  <si>
+    <t>"http://schema.org/CreativeWork"</t>
+  </si>
+  <si>
+    <t>The entity that identifies the crate and points at its root data entity.</t>
+  </si>
+  <si>
+    <t>"#hasSpecializedSchema"</t>
+  </si>
+  <si>
+    <t>#class_MainCollectionRoot</t>
+  </si>
+  <si>
+    <t>Main collection root</t>
+  </si>
+  <si>
+    <t>Dataset</t>
   </si>
   <si>
     <t>"http://schema.org/Dataset"</t>
   </si>
   <si>
-    <t>The root of any rocphotos crate: the collection root, a sub-collection directory, or the faces crate. Distinguished from the sub-collection Datasets a root crate lists by having hasPart of its own.</t>
+    <t>The root of the main collection crate. Told apart from the other two roots by what its hasPart holds: the sub-collection folders, and any albums.</t>
+  </si>
+  <si>
+    <t>#class_FolderCollectionRoot</t>
+  </si>
+  <si>
+    <t>Folder collection root</t>
+  </si>
+  <si>
+    <t>The root of a crate for one folder of photos. Told apart from the other two roots by its hasPart holding photos.</t>
+  </si>
+  <si>
+    <t>#class_FacesRoot</t>
+  </si>
+  <si>
+    <t>Faces crate root</t>
+  </si>
+  <si>
+    <t>The root of the faces crate. Told apart from the other two roots by its hasPart holding face embeddings.</t>
   </si>
   <si>
     <t>#class_SubCollection</t>
@@ -196,7 +248,7 @@
     <t>Sub-collection reference</t>
   </si>
   <si>
-    <t>How the root crate lists a sub-collection directory: a Dataset with a trailing-slash id and no hasPart of its own (its own crate holds the photos).</t>
+    <t>How the main collection root lists a sub-collection folder: a Dataset with a name and no hasPart of its own (its own crate holds the photos).</t>
   </si>
   <si>
     <t>#class_Photo</t>
@@ -205,6 +257,9 @@
     <t>Photo</t>
   </si>
   <si>
+    <t>ImageObject</t>
+  </si>
+  <si>
     <t>"http://schema.org/ImageObject"</t>
   </si>
   <si>
@@ -235,6 +290,9 @@
     <t>Album</t>
   </si>
   <si>
+    <t>ImageGallery</t>
+  </si>
+  <si>
     <t>"http://schema.org/ImageGallery"</t>
   </si>
   <si>
@@ -268,6 +326,9 @@
     <t>Pet</t>
   </si>
   <si>
+    <t>rocp:Pet</t>
+  </si>
+  <si>
     <t>"https://w3id.org/ldac/rocphotos/terms#Pet"</t>
   </si>
   <si>
@@ -289,6 +350,9 @@
     <t>Region (from the file's own tags)</t>
   </si>
   <si>
+    <t>ImageRegion</t>
+  </si>
+  <si>
     <t>"https://w3id.org/ldac/rocphotos/terms#ImageRegion"</t>
   </si>
   <si>
@@ -322,6 +386,9 @@
     <t>EXIF value</t>
   </si>
   <si>
+    <t>PropertyValue</t>
+  </si>
+  <si>
     <t>"http://schema.org/PropertyValue"</t>
   </si>
   <si>
@@ -334,61 +401,142 @@
     <t>Face embedding</t>
   </si>
   <si>
+    <t>FaceEmbedding</t>
+  </si>
+  <si>
     <t>"https://w3id.org/ldac/rocphotos/terms#FaceEmbedding"</t>
   </si>
   <si>
     <t>One reference embedding in the faces crate, for inspection — matching itself queries the companion SQLite index. Points back at the region it came from rather than holding image data.</t>
   </si>
   <si>
-    <t>rdfs:label</t>
+    <t>#SpouseRelationshipClass</t>
+  </si>
+  <si>
+    <t>Married</t>
+  </si>
+  <si>
+    <t>rico:SpouseRelation</t>
+  </si>
+  <si>
+    <t>"https://www.ica.org/standards/RiC/ontology#SpouseRelation"</t>
+  </si>
+  <si>
+    <t>Two people who are, or were, married to each other. Not oriented: it reads the same from either side. This is RiC's own SpouseRelation, used as it stands.</t>
+  </si>
+  <si>
+    <t>#ParentChildRelationshipClass</t>
+  </si>
+  <si>
+    <t>Parent and child</t>
+  </si>
+  <si>
+    <t>rico:ChildRelation</t>
+  </si>
+  <si>
+    <t>"https://www.ica.org/standards/RiC/ontology#ChildRelation"</t>
+  </si>
+  <si>
+    <t>Oriented from the parent to the child: the parent is the source, the child is the target. This is RiC's own ChildRelation, used as it stands, including its direction — which runs down a generation rather than up.</t>
   </si>
   <si>
     <t>domainIncludes</t>
   </si>
   <si>
-    <t>rdfs:comment</t>
-  </si>
-  <si>
     <t>rangeIncludes</t>
   </si>
   <si>
-    <t>#prop_root_name</t>
+    <t>#RO-Crate_Metadata_Descriptor.id</t>
   </si>
   <si>
     <t>rdf:Property</t>
   </si>
   <si>
+    <t>"#RO-Crate_Metadata_Descriptor"</t>
+  </si>
+  <si>
+    <t>Always ro-crate-metadata.json.</t>
+  </si>
+  <si>
+    <t>"#propertyValue_RO-Crate_Metadata_Descriptor.id"</t>
+  </si>
+  <si>
+    <t>#RO-Crate_Metadata_Descriptor.about</t>
+  </si>
+  <si>
+    <t>About</t>
+  </si>
+  <si>
+    <t>about</t>
+  </si>
+  <si>
+    <t>The one root data entity of this crate. Exactly one value, which must have the shape of one of the three kinds of root.</t>
+  </si>
+  <si>
+    <t>["#class_MainCollectionRoot", "#class_FolderCollectionRoot", "#class_FacesRoot"]</t>
+  </si>
+  <si>
+    <t>"http://schema.org/about"</t>
+  </si>
+  <si>
+    <t>#prop_mainroot_name</t>
+  </si>
+  <si>
+    <t>"#class_MainCollectionRoot"</t>
+  </si>
+  <si>
+    <t>The name of the collection, folder or crate.</t>
+  </si>
+  <si>
+    <t>"http://schema.org/Text"</t>
+  </si>
+  <si>
     <t>"http://schema.org/name"</t>
   </si>
   <si>
-    <t>"#Root_Data_Entity"</t>
-  </si>
-  <si>
-    <t>For a sub-collection, its path relative to the collection root.</t>
-  </si>
-  <si>
-    <t>"Text"</t>
-  </si>
-  <si>
-    <t>#prop_root_hasPart</t>
+    <t>#prop_mainroot_hasPart</t>
+  </si>
+  <si>
+    <t>Has part</t>
+  </si>
+  <si>
+    <t>Each sub-collection folder, as a Dataset reference, and each album.</t>
+  </si>
+  <si>
+    <t>["#class_SubCollection", "#class_Album"]</t>
   </si>
   <si>
     <t>"http://schema.org/hasPart"</t>
   </si>
   <si>
-    <t>The photos in this crate, or — in the root crate — each sub-collection Dataset and each album.</t>
-  </si>
-  <si>
-    <t>#prop_root_mentions</t>
-  </si>
-  <si>
-    <t>mentions</t>
-  </si>
-  <si>
-    <t>"http://schema.org/mentions"</t>
-  </si>
-  <si>
-    <t>Root crate only: every Person/Pet depicted anywhere in the collection. This is what makes them reachable in the graph, and where their description is meant to accumulate. Deliberately unrestricted in range: a Pet cannot be range-checked until rocphotos binds the rocphotos: prefix in its crates (see the profile text).</t>
+    <t>#prop_folderroot_name</t>
+  </si>
+  <si>
+    <t>"#class_FolderCollectionRoot"</t>
+  </si>
+  <si>
+    <t>#prop_folderroot_hasPart</t>
+  </si>
+  <si>
+    <t>Every photo in this folder.</t>
+  </si>
+  <si>
+    <t>"#class_Photo"</t>
+  </si>
+  <si>
+    <t>#prop_facesroot_name</t>
+  </si>
+  <si>
+    <t>"#class_FacesRoot"</t>
+  </si>
+  <si>
+    <t>#prop_facesroot_hasPart</t>
+  </si>
+  <si>
+    <t>Every face-recognition reference.</t>
+  </si>
+  <si>
+    <t>"#class_FaceEmbedding"</t>
   </si>
   <si>
     <t>#prop_subcollection_name</t>
@@ -400,162 +548,183 @@
     <t>The sub-collection's path, e.g. 2025/03/10.</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>#prop_photo_name</t>
   </si>
   <si>
-    <t>"#class_Photo"</t>
-  </si>
-  <si>
     <t>The file's own name.</t>
   </si>
   <si>
     <t>#prop_photo_title</t>
   </si>
   <si>
+    <t>Title</t>
+  </si>
+  <si>
     <t>title</t>
   </si>
   <si>
+    <t>Always present: the IPTC/XMP title if the file has one, its filename otherwise.</t>
+  </si>
+  <si>
     <t>"http://schema.org/title"</t>
   </si>
   <si>
-    <t>Always present: the IPTC/XMP title if the file has one, its filename otherwise.</t>
-  </si>
-  <si>
     <t>#prop_photo_description</t>
   </si>
   <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>The photo's own caption, if it has one.</t>
+  </si>
+  <si>
     <t>"http://schema.org/description"</t>
   </si>
   <si>
-    <t>The photo's own caption, if it has one.</t>
-  </si>
-  <si>
     <t>#prop_photo_dateCreated</t>
   </si>
   <si>
+    <t>Date created</t>
+  </si>
+  <si>
     <t>dateCreated</t>
   </si>
   <si>
+    <t>From EXIF DateTimeOriginal.</t>
+  </si>
+  <si>
+    <t>"http://schema.org/Date"</t>
+  </si>
+  <si>
     <t>"http://schema.org/dateCreated"</t>
   </si>
   <si>
-    <t>From EXIF DateTimeOriginal.</t>
-  </si>
-  <si>
-    <t>"Date"</t>
-  </si>
-  <si>
     <t>#prop_photo_dateModified</t>
   </si>
   <si>
+    <t>Date modified</t>
+  </si>
+  <si>
     <t>dateModified</t>
   </si>
   <si>
+    <t>The source file's modification time when last processed — what a rescan compares against to decide whether to re-read it.</t>
+  </si>
+  <si>
     <t>"http://schema.org/dateModified"</t>
   </si>
   <si>
-    <t>The source file's modification time when last processed — what a rescan compares against to decide whether to re-read it.</t>
-  </si>
-  <si>
     <t>#prop_photo_keywords</t>
   </si>
   <si>
+    <t>Keywords</t>
+  </si>
+  <si>
     <t>keywords</t>
   </si>
   <si>
+    <t>IPTC/XMP keywords, excluding any that duplicate a region's name.</t>
+  </si>
+  <si>
     <t>"http://schema.org/keywords"</t>
   </si>
   <si>
-    <t>IPTC/XMP keywords, excluding any that duplicate a region's name.</t>
-  </si>
-  <si>
     <t>#prop_photo_rating</t>
   </si>
   <si>
+    <t>Rating</t>
+  </si>
+  <si>
     <t>rating</t>
   </si>
   <si>
+    <t>XMP star rating, 1-5. Absent rather than 0 when unrated.</t>
+  </si>
+  <si>
+    <t>"http://schema.org/Number"</t>
+  </si>
+  <si>
     <t>"https://w3id.org/ldac/rocphotos/terms#rating"</t>
   </si>
   <si>
-    <t>XMP star rating, 1-5. Absent rather than 0 when unrated.</t>
-  </si>
-  <si>
-    <t>"Number"</t>
-  </si>
-  <si>
     <t>#prop_photo_exifData</t>
   </si>
   <si>
+    <t>EXIF data</t>
+  </si>
+  <si>
     <t>exifData</t>
   </si>
   <si>
+    <t>Selected EXIF fields, each as a PropertyValue.</t>
+  </si>
+  <si>
+    <t>"#class_ExifValue"</t>
+  </si>
+  <si>
     <t>"https://w3id.org/ldac/rocphotos/terms#exifData"</t>
   </si>
   <si>
-    <t>Selected EXIF fields, each as a PropertyValue.</t>
-  </si>
-  <si>
-    <t>"#class_ExifValue"</t>
-  </si>
-  <si>
     <t>#prop_photo_about</t>
   </si>
   <si>
-    <t>about</t>
-  </si>
-  <si>
-    <t>"http://schema.org/about"</t>
-  </si>
-  <si>
     <t>Everyone depicted, always via this crate's instance of them, never the shared identity directly.</t>
   </si>
   <si>
-    <t>["#InstancePersonClass", "#InstancePetClass"]</t>
+    <t>["#MainPersonClass", "#MainPetClass", "#InstancePersonClass", "#InstancePetClass"]</t>
   </si>
   <si>
     <t>#prop_photo_regions</t>
   </si>
   <si>
+    <t>Regions</t>
+  </si>
+  <si>
     <t>regions</t>
   </si>
   <si>
+    <t>Every tagged region on this photo, of either shape.</t>
+  </si>
+  <si>
+    <t>["#class_ImageRegion_Exif", "#class_ImageRegion_Standoff"]</t>
+  </si>
+  <si>
     <t>"https://w3id.org/ldac/rocphotos/terms#regions"</t>
   </si>
   <si>
-    <t>Every tagged region on this photo, of either shape.</t>
-  </si>
-  <si>
-    <t>["#class_ImageRegion_Exif", "#class_ImageRegion_Standoff"]</t>
-  </si>
-  <si>
     <t>#prop_photo_thumbnail</t>
   </si>
   <si>
     <t>thumbnail</t>
   </si>
   <si>
+    <t>The generated thumbnail.</t>
+  </si>
+  <si>
+    <t>"#class_Thumbnail"</t>
+  </si>
+  <si>
     <t>"http://schema.org/thumbnail"</t>
   </si>
   <si>
-    <t>The generated thumbnail.</t>
-  </si>
-  <si>
-    <t>"#class_Thumbnail"</t>
-  </si>
-  <si>
     <t>#prop_photo_processingError</t>
   </si>
   <si>
+    <t>Processing error</t>
+  </si>
+  <si>
     <t>processingError</t>
   </si>
   <si>
+    <t>An EXIF and/or thumbnail failure. Removed once the file processes cleanly.</t>
+  </si>
+  <si>
     <t>"https://w3id.org/ldac/rocphotos/terms#processingError"</t>
   </si>
   <si>
-    <t>An EXIF and/or thumbnail failure. Removed once the file processes cleanly.</t>
-  </si>
-  <si>
     <t>#prop_thumbnail_name</t>
   </si>
   <si>
@@ -565,15 +734,18 @@
     <t>#prop_albumitem_specializationOf</t>
   </si>
   <si>
+    <t>Specialization of</t>
+  </si>
+  <si>
+    <t>"#class_AlbumItem"</t>
+  </si>
+  <si>
+    <t>The real photo this item stands for. No range: the photo is described in its folder crate, not here, so it cannot be checked within this crate.</t>
+  </si>
+  <si>
     <t>"http://www.w3.org/ns/prov#specializationOf"</t>
   </si>
   <si>
-    <t>"#class_AlbumItem"</t>
-  </si>
-  <si>
-    <t>The real photo this item stands for.</t>
-  </si>
-  <si>
     <t>#prop_album_name</t>
   </si>
   <si>
@@ -601,30 +773,33 @@
     <t>"#MainPersonClass"</t>
   </si>
   <si>
+    <t>The main or canonical name for this person, this depends on the policy of a particular collection but may be their birth name or a nickname</t>
+  </si>
+  <si>
+    <t>#prop_personinstance_name</t>
+  </si>
+  <si>
+    <t>"#InstancePersonClass"</t>
+  </si>
+  <si>
+    <t>How they were known here, which need not match the shared identity's name.</t>
+  </si>
+  <si>
+    <t>#prop_personinstance_specializationOf</t>
+  </si>
+  <si>
+    <t>The shared identity this is an instance of.</t>
+  </si>
+  <si>
+    <t>#prop_pet_name</t>
+  </si>
+  <si>
+    <t>"#MainPetClass"</t>
+  </si>
+  <si>
     <t>The name their identity is derived from.</t>
   </si>
   <si>
-    <t>#prop_personinstance_name</t>
-  </si>
-  <si>
-    <t>"#InstancePersonClass"</t>
-  </si>
-  <si>
-    <t>How they were known here, which need not match the shared identity's name.</t>
-  </si>
-  <si>
-    <t>#prop_personinstance_specializationOf</t>
-  </si>
-  <si>
-    <t>The shared identity this is an instance of.</t>
-  </si>
-  <si>
-    <t>#prop_pet_name</t>
-  </si>
-  <si>
-    <t>"#MainPetClass"</t>
-  </si>
-  <si>
     <t>#prop_petinstance_name</t>
   </si>
   <si>
@@ -649,15 +824,18 @@
     <t>#prop_region_regionType</t>
   </si>
   <si>
+    <t>Region type</t>
+  </si>
+  <si>
     <t>regionType</t>
   </si>
   <si>
+    <t>A literal, either "Face" or "Pet".</t>
+  </si>
+  <si>
     <t>"https://w3id.org/ldac/rocphotos/terms#regionType"</t>
   </si>
   <si>
-    <t>A literal, either "Face" or "Pet".</t>
-  </si>
-  <si>
     <t>#prop_region_about</t>
   </si>
   <si>
@@ -667,51 +845,63 @@
     <t>#prop_region_xPosition</t>
   </si>
   <si>
+    <t>X position</t>
+  </si>
+  <si>
     <t>xPosition</t>
   </si>
   <si>
+    <t>The region's centre X, as a fraction of the image.</t>
+  </si>
+  <si>
     <t>"https://w3id.org/ldac/rocphotos/terms#xPosition"</t>
   </si>
   <si>
-    <t>The region's centre X, as a fraction of the image.</t>
-  </si>
-  <si>
     <t>#prop_region_yPosition</t>
   </si>
   <si>
+    <t>Y position</t>
+  </si>
+  <si>
     <t>yPosition</t>
   </si>
   <si>
+    <t>The region's centre Y, as a fraction of the image.</t>
+  </si>
+  <si>
     <t>"https://w3id.org/ldac/rocphotos/terms#yPosition"</t>
   </si>
   <si>
-    <t>The region's centre Y, as a fraction of the image.</t>
-  </si>
-  <si>
     <t>#prop_region_width</t>
   </si>
   <si>
+    <t>Width</t>
+  </si>
+  <si>
     <t>width</t>
   </si>
   <si>
+    <t>The region's width, as a fraction of the image.</t>
+  </si>
+  <si>
     <t>"http://schema.org/width"</t>
   </si>
   <si>
-    <t>The region's width, as a fraction of the image.</t>
-  </si>
-  <si>
     <t>#prop_region_height</t>
   </si>
   <si>
+    <t>Height</t>
+  </si>
+  <si>
     <t>height</t>
   </si>
   <si>
+    <t>The region's height, as a fraction of the image.</t>
+  </si>
+  <si>
     <t>"http://schema.org/height"</t>
   </si>
   <si>
-    <t>The region's height, as a fraction of the image.</t>
-  </si>
-  <si>
     <t>#prop_standoff_name</t>
   </si>
   <si>
@@ -727,66 +917,84 @@
     <t>#prop_standoff_hasTarget</t>
   </si>
   <si>
+    <t>Has target</t>
+  </si>
+  <si>
     <t>oa:hasTarget</t>
   </si>
   <si>
+    <t>A W3C Media Fragment on the photo — #xywh=percent:x,y,w,h, a top-left corner and size, unlike the centre-based EXIF shape.</t>
+  </si>
+  <si>
     <t>"http://www.w3.org/ns/oa#hasTarget"</t>
   </si>
   <si>
-    <t>A W3C Media Fragment on the photo — #xywh=percent:x,y,w,h, a top-left corner and size, unlike the centre-based EXIF shape.</t>
-  </si>
-  <si>
     <t>#prop_standoff_hasBody</t>
   </si>
   <si>
+    <t>Has body</t>
+  </si>
+  <si>
     <t>oa:hasBody</t>
   </si>
   <si>
+    <t>A per-region proxy for the subject, so this one sighting could later carry its own properties.</t>
+  </si>
+  <si>
+    <t>["#MainPersonClass", "#MainPetClass", "#class_RegionBody"]</t>
+  </si>
+  <si>
     <t>"http://www.w3.org/ns/oa#hasBody"</t>
   </si>
   <si>
-    <t>A per-region proxy for the subject, so this one sighting could later carry its own properties.</t>
+    <t>#prop_standoff_motivatedBy</t>
+  </si>
+  <si>
+    <t>Motivated by</t>
+  </si>
+  <si>
+    <t>oa:motivatedBy</t>
+  </si>
+  <si>
+    <t>Always oa:identifying — the annotation says who this is. The value comes from an ItemList so more motivations can be added later. As with any ItemList value, the crate must carry the oa:identifying entity itself, matching the one in this profile.</t>
+  </si>
+  <si>
+    <t>"#itemlist_motivation"</t>
+  </si>
+  <si>
+    <t>"http://www.w3.org/ns/oa#motivatedBy"</t>
+  </si>
+  <si>
+    <t>#prop_standoff_writtenToFile</t>
+  </si>
+  <si>
+    <t>Written to file</t>
+  </si>
+  <si>
+    <t>writtenToFile</t>
+  </si>
+  <si>
+    <t>Whether this region has been written into the photo file's own XMP. Once a rescan finds the same name in the file's real EXIF regions, this region is replaced by the EXIF-derived one.</t>
+  </si>
+  <si>
+    <t>"http://schema.org/Boolean"</t>
+  </si>
+  <si>
+    <t>"https://w3id.org/ldac/rocphotos/terms#writtenToFile"</t>
+  </si>
+  <si>
+    <t>#prop_regionbody_specializationOf</t>
   </si>
   <si>
     <t>"#class_RegionBody"</t>
   </si>
   <si>
-    <t>#prop_standoff_motivatedBy</t>
-  </si>
-  <si>
-    <t>oa:motivatedBy</t>
-  </si>
-  <si>
-    <t>"http://www.w3.org/ns/oa#motivatedBy"</t>
-  </si>
-  <si>
-    <t>Always oa:identifying — the annotation says who this is. The value comes from an ItemList so more motivations can be added later. As with any ItemList value, the crate must carry the oa:identifying entity itself, matching the one in this profile.</t>
-  </si>
-  <si>
-    <t>"#itemlist_motivation"</t>
-  </si>
-  <si>
-    <t>#prop_standoff_writtenToFile</t>
-  </si>
-  <si>
-    <t>writtenToFile</t>
-  </si>
-  <si>
-    <t>"https://w3id.org/ldac/rocphotos/terms#writtenToFile"</t>
-  </si>
-  <si>
-    <t>Whether this region has been written into the photo file's own XMP. Once a rescan finds the same name in the file's real EXIF regions, this region is replaced by the EXIF-derived one.</t>
-  </si>
-  <si>
-    <t>"Boolean"</t>
-  </si>
-  <si>
-    <t>#prop_regionbody_specializationOf</t>
-  </si>
-  <si>
     <t>This crate's instance of the person depicted.</t>
   </si>
   <si>
+    <t>["#MainPersonClass", "#InstancePersonClass"]</t>
+  </si>
+  <si>
     <t>#prop_exif_name</t>
   </si>
   <si>
@@ -799,85 +1007,232 @@
     <t>value</t>
   </si>
   <si>
+    <t>Its value, as text.</t>
+  </si>
+  <si>
     <t>"http://schema.org/value"</t>
   </si>
   <si>
-    <t>Its value, as text.</t>
-  </si>
-  <si>
     <t>#prop_embedding_name</t>
   </si>
   <si>
-    <t>"#class_FaceEmbedding"</t>
-  </si>
-  <si>
     <t>The person's name, or "Ignored stranger" for a permanently-suppressed face.</t>
   </si>
   <si>
     <t>#prop_embedding_about</t>
   </si>
   <si>
-    <t>The person this is a reference for. Absent entirely for a stranger.</t>
+    <t>The person this is a reference for. Absent entirely for a stranger. No range: the person is described in the main collection crate, not here, so it cannot be checked within this crate.</t>
   </si>
   <si>
     <t>#prop_embedding_sourceImage</t>
   </si>
   <si>
+    <t>Source image</t>
+  </si>
+  <si>
     <t>sourceImage</t>
   </si>
   <si>
+    <t>The photo it was computed from, as a collection-relative path.</t>
+  </si>
+  <si>
     <t>"https://w3id.org/ldac/rocphotos/terms#sourceImage"</t>
   </si>
   <si>
-    <t>The photo it was computed from, as a collection-relative path.</t>
-  </si>
-  <si>
     <t>#prop_embedding_sourceRegion</t>
   </si>
   <si>
+    <t>Source region</t>
+  </si>
+  <si>
     <t>sourceRegion</t>
   </si>
   <si>
+    <t>The region it was computed from. Absent for a stranger, which is never written back as a region.</t>
+  </si>
+  <si>
     <t>"https://w3id.org/ldac/rocphotos/terms#sourceRegion"</t>
   </si>
   <si>
-    <t>The region it was computed from. Absent for a stranger, which is never written back as a region.</t>
-  </si>
-  <si>
     <t>#prop_embedding_embedding</t>
   </si>
   <si>
+    <t>Embedding</t>
+  </si>
+  <si>
     <t>embedding</t>
   </si>
   <si>
+    <t>The model's own vector.</t>
+  </si>
+  <si>
     <t>"https://w3id.org/ldac/rocphotos/terms#embedding"</t>
   </si>
   <si>
-    <t>The model's own vector.</t>
-  </si>
-  <si>
     <t>#prop_embedding_model</t>
   </si>
   <si>
+    <t>Embedding model</t>
+  </si>
+  <si>
     <t>embeddingModel</t>
   </si>
   <si>
+    <t>The model that produced it.</t>
+  </si>
+  <si>
     <t>"https://w3id.org/ldac/rocphotos/terms#embeddingModel"</t>
   </si>
   <si>
-    <t>The model that produced it.</t>
-  </si>
-  <si>
     <t>#prop_embedding_modelVersion</t>
   </si>
   <si>
+    <t>Embedding model version</t>
+  </si>
+  <si>
     <t>embeddingModelVersion</t>
   </si>
   <si>
+    <t>Its version — a bump makes every reference obsolete, which is why it is recorded per entity.</t>
+  </si>
+  <si>
     <t>"https://w3id.org/ldac/rocphotos/terms#embeddingModelVersion"</t>
   </si>
   <si>
-    <t>Its version — a bump makes every reference obsolete, which is why it is recorded per entity.</t>
+    <t>#prop_person_description</t>
+  </si>
+  <si>
+    <t>Biographical notes about this person</t>
+  </si>
+  <si>
+    <t>#prop_person_birthDate</t>
+  </si>
+  <si>
+    <t>Birth date</t>
+  </si>
+  <si>
+    <t>birthDate</t>
+  </si>
+  <si>
+    <t>Date of birth for this person, to the maximum available precision - can use data ranges if this is not known</t>
+  </si>
+  <si>
+    <t>"http://schema.org/birthDate"</t>
+  </si>
+  <si>
+    <t>#prop_region_nameInFile</t>
+  </si>
+  <si>
+    <t>Name in file</t>
+  </si>
+  <si>
+    <t>nameInFile</t>
+  </si>
+  <si>
+    <t>The name the photo file's own tag gives this region, recorded only where it differs from the name the crate keeps. Its absence means the two agree.</t>
+  </si>
+  <si>
+    <t>#prop_spouse_connects</t>
+  </si>
+  <si>
+    <t>Spouses</t>
+  </si>
+  <si>
+    <t>rico:relationConnects</t>
+  </si>
+  <si>
+    <t>"#SpouseRelationshipClass"</t>
+  </si>
+  <si>
+    <t>The two people who are, or were, married to each other. Neither comes first: this relationship reads the same from either side.</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>"https://www.ica.org/standards/RiC/ontology#relationConnects"</t>
+  </si>
+  <si>
+    <t>#prop_parentchild_source</t>
+  </si>
+  <si>
+    <t>Parent</t>
+  </si>
+  <si>
+    <t>rico:relationHasSource</t>
+  </si>
+  <si>
+    <t>"#ParentChildRelationshipClass"</t>
+  </si>
+  <si>
+    <t>The parent. RiC orients this relationship from the parent, so the parent is its source.</t>
+  </si>
+  <si>
+    <t>"https://www.ica.org/standards/RiC/ontology#relationHasSource"</t>
+  </si>
+  <si>
+    <t>#prop_parentchild_target</t>
+  </si>
+  <si>
+    <t>Child</t>
+  </si>
+  <si>
+    <t>rico:relationHasTarget</t>
+  </si>
+  <si>
+    <t>The child, who is the target of the relationship.</t>
+  </si>
+  <si>
+    <t>"https://www.ica.org/standards/RiC/ontology#relationHasTarget"</t>
+  </si>
+  <si>
+    <t>#prop_spouse_beginningDate</t>
+  </si>
+  <si>
+    <t>Began</t>
+  </si>
+  <si>
+    <t>rico:beginningDate</t>
+  </si>
+  <si>
+    <t>When it began, to whatever precision is known — a year on its own is fine.</t>
+  </si>
+  <si>
+    <t>"https://www.ica.org/standards/RiC/ontology#beginningDate"</t>
+  </si>
+  <si>
+    <t>#prop_spouse_endDate</t>
+  </si>
+  <si>
+    <t>Ended</t>
+  </si>
+  <si>
+    <t>rico:endDate</t>
+  </si>
+  <si>
+    <t>When it ended, if it has. Left out while it still holds.</t>
+  </si>
+  <si>
+    <t>"https://www.ica.org/standards/RiC/ontology#endDate"</t>
+  </si>
+  <si>
+    <t>#prop_parentchild_beginningDate</t>
+  </si>
+  <si>
+    <t>#prop_parentchild_endDate</t>
+  </si>
+  <si>
+    <t>#propertyValue_RO-Crate_Metadata_Descriptor.id</t>
+  </si>
+  <si>
+    <t>RO-Crate Metadata Descriptor identifier</t>
+  </si>
+  <si>
+    <t>The fixed @id of the RO-Crate Metadata Descriptor.</t>
+  </si>
+  <si>
+    <t>ro-crate-metadata.json</t>
   </si>
   <si>
     <t>itemListElement</t>
@@ -1395,6 +1750,60 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="6" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>404</v>
+      </c>
+      <c r="F1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>405</v>
+      </c>
+      <c r="B2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D2" t="s">
+        <v>408</v>
+      </c>
+      <c r="E2" t="s">
+        <v>409</v>
+      </c>
+      <c r="F2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -1417,16 +1826,16 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>292</v>
+        <v>410</v>
       </c>
       <c r="B2" t="s">
-        <v>293</v>
+        <v>411</v>
       </c>
       <c r="C2" t="s">
-        <v>294</v>
+        <v>412</v>
       </c>
       <c r="D2" t="s">
-        <v>295</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -1476,13 +1885,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="3" width="20" customWidth="1"/>
+    <col min="1" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1492,16 +1901,22 @@
       <c r="C1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="D2" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1531,10 +1946,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
         <v>26</v>
@@ -1565,21 +1980,21 @@
         <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1607,44 +2022,44 @@
         <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E1" t="s">
         <v>22</v>
       </c>
       <c r="F1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F3" t="s">
         <v>23</v>
@@ -1658,13 +2073,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="7" width="20" customWidth="1"/>
+    <col min="1" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1675,277 +2090,539 @@
         <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
+        <v>59</v>
+      </c>
+      <c r="F2" t="s">
+        <v>60</v>
       </c>
       <c r="G2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" t="s">
         <v>56</v>
       </c>
-      <c r="B3" t="s">
-        <v>52</v>
-      </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+      <c r="F3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+      <c r="F4" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" t="s">
         <v>64</v>
-      </c>
-      <c r="D5" t="s">
-        <v>61</v>
       </c>
       <c r="E5" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" t="s">
+        <v>72</v>
+      </c>
+      <c r="I5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+      <c r="F6" t="s">
+        <v>75</v>
+      </c>
+      <c r="I6" t="s">
+        <v>61</v>
+      </c>
+      <c r="J6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="F7" t="s">
+        <v>80</v>
+      </c>
+      <c r="I7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="F8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I8" t="s">
+        <v>61</v>
+      </c>
+      <c r="J8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" t="s">
         <v>78</v>
-      </c>
-      <c r="D9" t="s">
-        <v>75</v>
       </c>
       <c r="E9" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I9" t="s">
+        <v>61</v>
+      </c>
+      <c r="J9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="E10" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="F10" t="s">
+        <v>91</v>
+      </c>
+      <c r="I10" t="s">
+        <v>61</v>
+      </c>
+      <c r="J10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="E11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+      <c r="F11" t="s">
+        <v>95</v>
+      </c>
+      <c r="I11" t="s">
+        <v>61</v>
+      </c>
+      <c r="J11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+      <c r="F12" t="s">
+        <v>98</v>
+      </c>
+      <c r="I12" t="s">
+        <v>61</v>
+      </c>
+      <c r="J12" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
+        <v>101</v>
+      </c>
+      <c r="E13" t="s">
+        <v>102</v>
+      </c>
+      <c r="F13" t="s">
+        <v>103</v>
+      </c>
+      <c r="I13" t="s">
+        <v>61</v>
+      </c>
+      <c r="J13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>104</v>
+      </c>
+      <c r="B14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D14" t="s">
+        <v>101</v>
+      </c>
+      <c r="E14" t="s">
+        <v>102</v>
+      </c>
+      <c r="F14" t="s">
+        <v>106</v>
+      </c>
+      <c r="I14" t="s">
+        <v>61</v>
+      </c>
+      <c r="J14" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>107</v>
+      </c>
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>108</v>
+      </c>
+      <c r="D15" t="s">
+        <v>109</v>
+      </c>
+      <c r="E15" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" t="s">
+        <v>111</v>
+      </c>
+      <c r="I15" t="s">
+        <v>61</v>
+      </c>
+      <c r="J15" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" t="s">
+        <v>113</v>
+      </c>
+      <c r="D16" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" t="s">
+        <v>114</v>
+      </c>
+      <c r="F16" t="s">
+        <v>115</v>
+      </c>
+      <c r="I16" t="s">
+        <v>61</v>
+      </c>
+      <c r="J16" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" t="s">
+        <v>117</v>
+      </c>
+      <c r="D17" t="s">
         <v>93</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E17" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>95</v>
-      </c>
-      <c r="B14" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D14" t="s">
-        <v>75</v>
-      </c>
-      <c r="E14" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>98</v>
-      </c>
-      <c r="B15" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" t="s">
-        <v>99</v>
-      </c>
-      <c r="D15" t="s">
-        <v>100</v>
-      </c>
-      <c r="E15" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>102</v>
-      </c>
-      <c r="B16" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" t="s">
-        <v>103</v>
-      </c>
-      <c r="D16" t="s">
-        <v>104</v>
-      </c>
-      <c r="E16" t="s">
-        <v>105</v>
+      <c r="F17" t="s">
+        <v>118</v>
+      </c>
+      <c r="I17" t="s">
+        <v>61</v>
+      </c>
+      <c r="J17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>119</v>
+      </c>
+      <c r="B18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" t="s">
+        <v>120</v>
+      </c>
+      <c r="D18" t="s">
+        <v>121</v>
+      </c>
+      <c r="E18" t="s">
+        <v>122</v>
+      </c>
+      <c r="F18" t="s">
+        <v>123</v>
+      </c>
+      <c r="I18" t="s">
+        <v>61</v>
+      </c>
+      <c r="J18" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>124</v>
+      </c>
+      <c r="B19" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" t="s">
+        <v>125</v>
+      </c>
+      <c r="D19" t="s">
+        <v>126</v>
+      </c>
+      <c r="E19" t="s">
+        <v>127</v>
+      </c>
+      <c r="F19" t="s">
+        <v>128</v>
+      </c>
+      <c r="I19" t="s">
+        <v>61</v>
+      </c>
+      <c r="J19" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>129</v>
+      </c>
+      <c r="B20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" t="s">
+        <v>130</v>
+      </c>
+      <c r="D20" t="s">
+        <v>131</v>
+      </c>
+      <c r="E20" t="s">
+        <v>132</v>
+      </c>
+      <c r="F20" t="s">
+        <v>133</v>
+      </c>
+      <c r="I20" t="s">
+        <v>61</v>
+      </c>
+      <c r="J20" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>134</v>
+      </c>
+      <c r="B21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" t="s">
+        <v>135</v>
+      </c>
+      <c r="D21" t="s">
+        <v>136</v>
+      </c>
+      <c r="E21" t="s">
+        <v>137</v>
+      </c>
+      <c r="F21" t="s">
+        <v>138</v>
+      </c>
+      <c r="I21" t="s">
+        <v>61</v>
+      </c>
+      <c r="J21" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -1956,13 +2633,13 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="9" width="20" customWidth="1"/>
+    <col min="1" max="11" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1973,1421 +2650,2066 @@
         <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="E1" t="s">
-        <v>48</v>
+        <v>139</v>
       </c>
       <c r="F1" t="s">
-        <v>107</v>
+        <v>52</v>
       </c>
       <c r="G1" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H1" t="s">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="I1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+      <c r="J1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="F2" t="s">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="G2" t="s">
-        <v>114</v>
-      </c>
-      <c r="H2" t="s">
-        <v>115</v>
+        <v>145</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="B3" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>147</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>148</v>
       </c>
       <c r="E3" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="F3" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="G3" t="s">
-        <v>118</v>
+        <v>150</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
       </c>
       <c r="I3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J3" t="s">
+        <v>61</v>
+      </c>
+      <c r="K3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>119</v>
+        <v>152</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="C4" t="s">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="D4" t="s">
-        <v>120</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>121</v>
+        <v>153</v>
       </c>
       <c r="F4" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="G4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
+        <v>61</v>
+      </c>
+      <c r="K4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>123</v>
+        <v>157</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>158</v>
       </c>
       <c r="D5" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>112</v>
+        <v>153</v>
       </c>
       <c r="F5" t="s">
-        <v>124</v>
+        <v>159</v>
       </c>
       <c r="G5" t="s">
-        <v>125</v>
-      </c>
-      <c r="H5" t="s">
-        <v>115</v>
-      </c>
-      <c r="I5">
+        <v>160</v>
+      </c>
+      <c r="H5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J5" t="s">
+        <v>61</v>
+      </c>
+      <c r="K5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>126</v>
+        <v>162</v>
       </c>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D6" t="s">
         <v>6</v>
       </c>
       <c r="E6" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="F6" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="G6" t="s">
-        <v>128</v>
-      </c>
-      <c r="H6" t="s">
-        <v>115</v>
-      </c>
-      <c r="I6">
+        <v>155</v>
+      </c>
+      <c r="H6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J6" t="s">
+        <v>61</v>
+      </c>
+      <c r="K6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>129</v>
+        <v>164</v>
       </c>
       <c r="B7" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="C7" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="D7" t="s">
-        <v>130</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>131</v>
+        <v>163</v>
       </c>
       <c r="F7" t="s">
-        <v>127</v>
+        <v>165</v>
       </c>
       <c r="G7" t="s">
-        <v>132</v>
-      </c>
-      <c r="H7" t="s">
-        <v>115</v>
-      </c>
-      <c r="I7">
+        <v>166</v>
+      </c>
+      <c r="H7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J7" t="s">
+        <v>61</v>
+      </c>
+      <c r="K7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>133</v>
+        <v>167</v>
       </c>
       <c r="B8" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="C8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" t="s">
+        <v>168</v>
+      </c>
+      <c r="F8" t="s">
+        <v>154</v>
+      </c>
+      <c r="G8" t="s">
+        <v>155</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="J8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K8" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>169</v>
+      </c>
+      <c r="B9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C9" t="s">
+        <v>158</v>
+      </c>
+      <c r="D9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G9" t="s">
+        <v>171</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="J9" t="s">
+        <v>61</v>
+      </c>
+      <c r="K9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>172</v>
+      </c>
+      <c r="B10" t="s">
+        <v>142</v>
+      </c>
+      <c r="C10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F10" t="s">
+        <v>174</v>
+      </c>
+      <c r="G10" t="s">
+        <v>155</v>
+      </c>
+      <c r="H10" t="s">
+        <v>175</v>
+      </c>
+      <c r="J10" t="s">
+        <v>61</v>
+      </c>
+      <c r="K10" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>176</v>
+      </c>
+      <c r="B11" t="s">
+        <v>142</v>
+      </c>
+      <c r="C11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" t="s">
+        <v>166</v>
+      </c>
+      <c r="F11" t="s">
+        <v>177</v>
+      </c>
+      <c r="G11" t="s">
+        <v>155</v>
+      </c>
+      <c r="H11" t="s">
+        <v>175</v>
+      </c>
+      <c r="J11" t="s">
+        <v>61</v>
+      </c>
+      <c r="K11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>178</v>
+      </c>
+      <c r="B12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C12" t="s">
+        <v>179</v>
+      </c>
+      <c r="D12" t="s">
+        <v>180</v>
+      </c>
+      <c r="E12" t="s">
+        <v>166</v>
+      </c>
+      <c r="F12" t="s">
+        <v>181</v>
+      </c>
+      <c r="G12" t="s">
+        <v>155</v>
+      </c>
+      <c r="H12" t="s">
+        <v>175</v>
+      </c>
+      <c r="J12" t="s">
+        <v>61</v>
+      </c>
+      <c r="K12" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>183</v>
+      </c>
+      <c r="B13" t="s">
+        <v>142</v>
+      </c>
+      <c r="C13" t="s">
+        <v>184</v>
+      </c>
+      <c r="D13" t="s">
         <v>8</v>
       </c>
-      <c r="D8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" t="s">
-        <v>134</v>
-      </c>
-      <c r="F8" t="s">
-        <v>127</v>
-      </c>
-      <c r="G8" t="s">
-        <v>135</v>
-      </c>
-      <c r="H8" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>136</v>
-      </c>
-      <c r="B9" t="s">
-        <v>111</v>
-      </c>
-      <c r="C9" t="s">
-        <v>137</v>
-      </c>
-      <c r="D9" t="s">
-        <v>137</v>
-      </c>
-      <c r="E9" t="s">
-        <v>138</v>
-      </c>
-      <c r="F9" t="s">
-        <v>127</v>
-      </c>
-      <c r="G9" t="s">
-        <v>139</v>
-      </c>
-      <c r="H9" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>141</v>
-      </c>
-      <c r="B10" t="s">
-        <v>111</v>
-      </c>
-      <c r="C10" t="s">
-        <v>142</v>
-      </c>
-      <c r="D10" t="s">
-        <v>142</v>
-      </c>
-      <c r="E10" t="s">
-        <v>143</v>
-      </c>
-      <c r="F10" t="s">
-        <v>127</v>
-      </c>
-      <c r="G10" t="s">
-        <v>144</v>
-      </c>
-      <c r="H10" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>145</v>
-      </c>
-      <c r="B11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C11" t="s">
-        <v>146</v>
-      </c>
-      <c r="D11" t="s">
-        <v>146</v>
-      </c>
-      <c r="E11" t="s">
-        <v>147</v>
-      </c>
-      <c r="F11" t="s">
-        <v>127</v>
-      </c>
-      <c r="G11" t="s">
-        <v>148</v>
-      </c>
-      <c r="H11" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>149</v>
-      </c>
-      <c r="B12" t="s">
-        <v>111</v>
-      </c>
-      <c r="C12" t="s">
-        <v>150</v>
-      </c>
-      <c r="D12" t="s">
-        <v>150</v>
-      </c>
-      <c r="E12" t="s">
-        <v>151</v>
-      </c>
-      <c r="F12" t="s">
-        <v>127</v>
-      </c>
-      <c r="G12" t="s">
-        <v>152</v>
-      </c>
-      <c r="H12" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>154</v>
-      </c>
-      <c r="B13" t="s">
-        <v>111</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="E13" t="s">
+        <v>166</v>
+      </c>
+      <c r="F13" t="s">
+        <v>185</v>
+      </c>
+      <c r="G13" t="s">
         <v>155</v>
       </c>
-      <c r="D13" t="s">
-        <v>155</v>
-      </c>
-      <c r="E13" t="s">
-        <v>156</v>
-      </c>
-      <c r="F13" t="s">
-        <v>127</v>
-      </c>
-      <c r="G13" t="s">
-        <v>157</v>
-      </c>
-      <c r="H13" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J13" t="s">
+        <v>61</v>
+      </c>
+      <c r="K13" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>159</v>
+        <v>187</v>
       </c>
       <c r="B14" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="C14" t="s">
-        <v>160</v>
+        <v>188</v>
       </c>
       <c r="D14" t="s">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="E14" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="F14" t="s">
-        <v>127</v>
+        <v>190</v>
       </c>
       <c r="G14" t="s">
-        <v>162</v>
-      </c>
-      <c r="H14" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+      <c r="J14" t="s">
+        <v>61</v>
+      </c>
+      <c r="K14" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="B15" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="C15" t="s">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="D15" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="E15" t="s">
         <v>166</v>
       </c>
       <c r="F15" t="s">
-        <v>127</v>
+        <v>196</v>
       </c>
       <c r="G15" t="s">
-        <v>167</v>
-      </c>
-      <c r="H15" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+      <c r="J15" t="s">
+        <v>61</v>
+      </c>
+      <c r="K15" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="B16" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="C16" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="D16" t="s">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="E16" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F16" t="s">
-        <v>127</v>
+        <v>201</v>
       </c>
       <c r="G16" t="s">
-        <v>172</v>
-      </c>
-      <c r="H16" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+      <c r="J16" t="s">
+        <v>61</v>
+      </c>
+      <c r="K16" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="B17" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="C17" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="D17" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="E17" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="F17" t="s">
-        <v>127</v>
+        <v>206</v>
       </c>
       <c r="G17" t="s">
-        <v>177</v>
-      </c>
-      <c r="H17" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+      <c r="J17" t="s">
+        <v>61</v>
+      </c>
+      <c r="K17" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>178</v>
+        <v>209</v>
       </c>
       <c r="B18" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="C18" t="s">
-        <v>6</v>
+        <v>210</v>
       </c>
       <c r="D18" t="s">
-        <v>6</v>
+        <v>211</v>
       </c>
       <c r="E18" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="F18" t="s">
-        <v>173</v>
+        <v>212</v>
       </c>
       <c r="G18" t="s">
-        <v>179</v>
-      </c>
-      <c r="H18" t="s">
-        <v>115</v>
-      </c>
-      <c r="I18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+      <c r="J18" t="s">
+        <v>61</v>
+      </c>
+      <c r="K18" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="C19" t="s">
-        <v>48</v>
+        <v>147</v>
       </c>
       <c r="D19" t="s">
-        <v>48</v>
+        <v>148</v>
       </c>
       <c r="E19" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="F19" t="s">
-        <v>182</v>
+        <v>216</v>
       </c>
       <c r="G19" t="s">
-        <v>183</v>
-      </c>
-      <c r="H19" t="s">
-        <v>127</v>
-      </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+      <c r="J19" t="s">
+        <v>61</v>
+      </c>
+      <c r="K19" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>184</v>
+        <v>218</v>
       </c>
       <c r="B20" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="C20" t="s">
-        <v>6</v>
+        <v>219</v>
       </c>
       <c r="D20" t="s">
-        <v>6</v>
+        <v>220</v>
       </c>
       <c r="E20" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="F20" t="s">
-        <v>185</v>
+        <v>221</v>
       </c>
       <c r="G20" t="s">
-        <v>186</v>
-      </c>
-      <c r="H20" t="s">
-        <v>115</v>
-      </c>
-      <c r="I20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+      <c r="J20" t="s">
+        <v>61</v>
+      </c>
+      <c r="K20" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>187</v>
+        <v>224</v>
       </c>
       <c r="B21" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="C21" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="D21" t="s">
-        <v>8</v>
+        <v>225</v>
       </c>
       <c r="E21" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
       <c r="F21" t="s">
-        <v>185</v>
+        <v>226</v>
       </c>
       <c r="G21" t="s">
-        <v>188</v>
-      </c>
-      <c r="H21" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+      <c r="J21" t="s">
+        <v>61</v>
+      </c>
+      <c r="K21" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>189</v>
+        <v>229</v>
       </c>
       <c r="B22" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>230</v>
       </c>
       <c r="D22" t="s">
-        <v>22</v>
+        <v>231</v>
       </c>
       <c r="E22" t="s">
-        <v>117</v>
+        <v>166</v>
       </c>
       <c r="F22" t="s">
-        <v>185</v>
+        <v>232</v>
       </c>
       <c r="G22" t="s">
-        <v>190</v>
-      </c>
-      <c r="H22" t="s">
-        <v>182</v>
-      </c>
-      <c r="I22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+      <c r="J22" t="s">
+        <v>61</v>
+      </c>
+      <c r="K22" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>191</v>
+        <v>234</v>
       </c>
       <c r="B23" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="C23" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D23" t="s">
         <v>6</v>
       </c>
       <c r="E23" t="s">
-        <v>112</v>
+        <v>227</v>
       </c>
       <c r="F23" t="s">
-        <v>192</v>
+        <v>235</v>
       </c>
       <c r="G23" t="s">
-        <v>193</v>
+        <v>155</v>
       </c>
       <c r="H23" t="s">
-        <v>115</v>
-      </c>
-      <c r="I23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+      <c r="J23" t="s">
+        <v>61</v>
+      </c>
+      <c r="K23" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>194</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="C24" t="s">
+        <v>237</v>
+      </c>
+      <c r="D24" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" t="s">
+        <v>238</v>
+      </c>
+      <c r="F24" t="s">
+        <v>239</v>
+      </c>
+      <c r="H24" t="s">
+        <v>175</v>
+      </c>
+      <c r="J24" t="s">
+        <v>61</v>
+      </c>
+      <c r="K24" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>241</v>
+      </c>
+      <c r="B25" t="s">
+        <v>142</v>
+      </c>
+      <c r="C25" t="s">
+        <v>0</v>
+      </c>
+      <c r="D25" t="s">
         <v>6</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E25" t="s">
+        <v>242</v>
+      </c>
+      <c r="F25" t="s">
+        <v>243</v>
+      </c>
+      <c r="G25" t="s">
+        <v>155</v>
+      </c>
+      <c r="H25" t="s">
+        <v>175</v>
+      </c>
+      <c r="J25" t="s">
+        <v>61</v>
+      </c>
+      <c r="K25" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>244</v>
+      </c>
+      <c r="B26" t="s">
+        <v>142</v>
+      </c>
+      <c r="C26" t="s">
+        <v>184</v>
+      </c>
+      <c r="D26" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" t="s">
+        <v>242</v>
+      </c>
+      <c r="F26" t="s">
+        <v>245</v>
+      </c>
+      <c r="G26" t="s">
+        <v>155</v>
+      </c>
+      <c r="J26" t="s">
+        <v>61</v>
+      </c>
+      <c r="K26" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>246</v>
+      </c>
+      <c r="B27" t="s">
+        <v>142</v>
+      </c>
+      <c r="C27" t="s">
+        <v>158</v>
+      </c>
+      <c r="D27" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" t="s">
+        <v>242</v>
+      </c>
+      <c r="F27" t="s">
+        <v>247</v>
+      </c>
+      <c r="G27" t="s">
+        <v>238</v>
+      </c>
+      <c r="H27" t="s">
+        <v>175</v>
+      </c>
+      <c r="J27" t="s">
+        <v>61</v>
+      </c>
+      <c r="K27" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>248</v>
+      </c>
+      <c r="B28" t="s">
+        <v>142</v>
+      </c>
+      <c r="C28" t="s">
+        <v>0</v>
+      </c>
+      <c r="D28" t="s">
         <v>6</v>
       </c>
-      <c r="E24" t="s">
-        <v>112</v>
-      </c>
-      <c r="F24" t="s">
-        <v>195</v>
-      </c>
-      <c r="G24" t="s">
-        <v>196</v>
-      </c>
-      <c r="H24" t="s">
-        <v>115</v>
-      </c>
-      <c r="I24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>197</v>
-      </c>
-      <c r="B25" t="s">
-        <v>111</v>
-      </c>
-      <c r="C25" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" t="s">
-        <v>48</v>
-      </c>
-      <c r="E25" t="s">
-        <v>181</v>
-      </c>
-      <c r="F25" t="s">
-        <v>195</v>
-      </c>
-      <c r="G25" t="s">
-        <v>198</v>
-      </c>
-      <c r="H25" t="s">
-        <v>192</v>
-      </c>
-      <c r="I25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>199</v>
-      </c>
-      <c r="B26" t="s">
-        <v>111</v>
-      </c>
-      <c r="C26" t="s">
-        <v>6</v>
-      </c>
-      <c r="D26" t="s">
-        <v>6</v>
-      </c>
-      <c r="E26" t="s">
-        <v>112</v>
-      </c>
-      <c r="F26" t="s">
-        <v>200</v>
-      </c>
-      <c r="G26" t="s">
-        <v>193</v>
-      </c>
-      <c r="H26" t="s">
-        <v>115</v>
-      </c>
-      <c r="I26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>201</v>
-      </c>
-      <c r="B27" t="s">
-        <v>111</v>
-      </c>
-      <c r="C27" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" t="s">
-        <v>6</v>
-      </c>
-      <c r="E27" t="s">
-        <v>112</v>
-      </c>
-      <c r="F27" t="s">
-        <v>202</v>
-      </c>
-      <c r="G27" t="s">
-        <v>203</v>
-      </c>
-      <c r="H27" t="s">
-        <v>115</v>
-      </c>
-      <c r="I27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>204</v>
-      </c>
-      <c r="B28" t="s">
-        <v>111</v>
-      </c>
-      <c r="C28" t="s">
-        <v>48</v>
-      </c>
-      <c r="D28" t="s">
-        <v>48</v>
-      </c>
       <c r="E28" t="s">
-        <v>181</v>
+        <v>249</v>
       </c>
       <c r="F28" t="s">
-        <v>202</v>
+        <v>250</v>
       </c>
       <c r="G28" t="s">
-        <v>198</v>
+        <v>155</v>
       </c>
       <c r="H28" t="s">
-        <v>200</v>
-      </c>
-      <c r="I28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+      <c r="J28" t="s">
+        <v>61</v>
+      </c>
+      <c r="K28" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>205</v>
+        <v>251</v>
       </c>
       <c r="B29" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="C29" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D29" t="s">
         <v>6</v>
       </c>
       <c r="E29" t="s">
-        <v>112</v>
+        <v>252</v>
       </c>
       <c r="F29" t="s">
-        <v>206</v>
+        <v>253</v>
       </c>
       <c r="G29" t="s">
+        <v>155</v>
+      </c>
+      <c r="H29" t="s">
+        <v>175</v>
+      </c>
+      <c r="J29" t="s">
+        <v>61</v>
+      </c>
+      <c r="K29" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>254</v>
+      </c>
+      <c r="B30" t="s">
+        <v>142</v>
+      </c>
+      <c r="C30" t="s">
+        <v>237</v>
+      </c>
+      <c r="D30" t="s">
+        <v>51</v>
+      </c>
+      <c r="E30" t="s">
+        <v>252</v>
+      </c>
+      <c r="F30" t="s">
+        <v>255</v>
+      </c>
+      <c r="G30" t="s">
+        <v>249</v>
+      </c>
+      <c r="H30" t="s">
+        <v>175</v>
+      </c>
+      <c r="J30" t="s">
+        <v>61</v>
+      </c>
+      <c r="K30" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>256</v>
+      </c>
+      <c r="B31" t="s">
+        <v>142</v>
+      </c>
+      <c r="C31" t="s">
+        <v>0</v>
+      </c>
+      <c r="D31" t="s">
+        <v>6</v>
+      </c>
+      <c r="E31" t="s">
+        <v>257</v>
+      </c>
+      <c r="F31" t="s">
+        <v>258</v>
+      </c>
+      <c r="G31" t="s">
+        <v>155</v>
+      </c>
+      <c r="H31" t="s">
+        <v>175</v>
+      </c>
+      <c r="J31" t="s">
+        <v>61</v>
+      </c>
+      <c r="K31" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>259</v>
+      </c>
+      <c r="B32" t="s">
+        <v>142</v>
+      </c>
+      <c r="C32" t="s">
+        <v>0</v>
+      </c>
+      <c r="D32" t="s">
+        <v>6</v>
+      </c>
+      <c r="E32" t="s">
+        <v>260</v>
+      </c>
+      <c r="F32" t="s">
+        <v>261</v>
+      </c>
+      <c r="G32" t="s">
+        <v>155</v>
+      </c>
+      <c r="H32" t="s">
+        <v>175</v>
+      </c>
+      <c r="J32" t="s">
+        <v>61</v>
+      </c>
+      <c r="K32" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>262</v>
+      </c>
+      <c r="B33" t="s">
+        <v>142</v>
+      </c>
+      <c r="C33" t="s">
+        <v>237</v>
+      </c>
+      <c r="D33" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" t="s">
+        <v>260</v>
+      </c>
+      <c r="F33" t="s">
+        <v>255</v>
+      </c>
+      <c r="G33" t="s">
+        <v>257</v>
+      </c>
+      <c r="H33" t="s">
+        <v>175</v>
+      </c>
+      <c r="J33" t="s">
+        <v>61</v>
+      </c>
+      <c r="K33" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>263</v>
+      </c>
+      <c r="B34" t="s">
+        <v>142</v>
+      </c>
+      <c r="C34" t="s">
+        <v>0</v>
+      </c>
+      <c r="D34" t="s">
+        <v>6</v>
+      </c>
+      <c r="E34" t="s">
+        <v>264</v>
+      </c>
+      <c r="F34" t="s">
+        <v>265</v>
+      </c>
+      <c r="G34" t="s">
+        <v>155</v>
+      </c>
+      <c r="H34" t="s">
+        <v>175</v>
+      </c>
+      <c r="J34" t="s">
+        <v>61</v>
+      </c>
+      <c r="K34" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>266</v>
+      </c>
+      <c r="B35" t="s">
+        <v>142</v>
+      </c>
+      <c r="C35" t="s">
+        <v>267</v>
+      </c>
+      <c r="D35" t="s">
+        <v>268</v>
+      </c>
+      <c r="E35" t="s">
+        <v>264</v>
+      </c>
+      <c r="F35" t="s">
+        <v>269</v>
+      </c>
+      <c r="G35" t="s">
+        <v>155</v>
+      </c>
+      <c r="H35" t="s">
+        <v>175</v>
+      </c>
+      <c r="J35" t="s">
+        <v>61</v>
+      </c>
+      <c r="K35" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>271</v>
+      </c>
+      <c r="B36" t="s">
+        <v>142</v>
+      </c>
+      <c r="C36" t="s">
+        <v>147</v>
+      </c>
+      <c r="D36" t="s">
+        <v>148</v>
+      </c>
+      <c r="E36" t="s">
+        <v>264</v>
+      </c>
+      <c r="F36" t="s">
+        <v>272</v>
+      </c>
+      <c r="G36" t="s">
+        <v>217</v>
+      </c>
+      <c r="H36" t="s">
+        <v>175</v>
+      </c>
+      <c r="J36" t="s">
+        <v>61</v>
+      </c>
+      <c r="K36" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>273</v>
+      </c>
+      <c r="B37" t="s">
+        <v>142</v>
+      </c>
+      <c r="C37" t="s">
+        <v>274</v>
+      </c>
+      <c r="D37" t="s">
+        <v>275</v>
+      </c>
+      <c r="E37" t="s">
+        <v>264</v>
+      </c>
+      <c r="F37" t="s">
+        <v>276</v>
+      </c>
+      <c r="G37" t="s">
         <v>207</v>
       </c>
-      <c r="H29" t="s">
-        <v>115</v>
-      </c>
-      <c r="I29">
+      <c r="H37" t="s">
+        <v>175</v>
+      </c>
+      <c r="J37" t="s">
+        <v>61</v>
+      </c>
+      <c r="K37" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>278</v>
+      </c>
+      <c r="B38" t="s">
+        <v>142</v>
+      </c>
+      <c r="C38" t="s">
+        <v>279</v>
+      </c>
+      <c r="D38" t="s">
+        <v>280</v>
+      </c>
+      <c r="E38" t="s">
+        <v>264</v>
+      </c>
+      <c r="F38" t="s">
+        <v>281</v>
+      </c>
+      <c r="G38" t="s">
+        <v>207</v>
+      </c>
+      <c r="H38" t="s">
+        <v>175</v>
+      </c>
+      <c r="J38" t="s">
+        <v>61</v>
+      </c>
+      <c r="K38" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>283</v>
+      </c>
+      <c r="B39" t="s">
+        <v>142</v>
+      </c>
+      <c r="C39" t="s">
+        <v>284</v>
+      </c>
+      <c r="D39" t="s">
+        <v>285</v>
+      </c>
+      <c r="E39" t="s">
+        <v>264</v>
+      </c>
+      <c r="F39" t="s">
+        <v>286</v>
+      </c>
+      <c r="G39" t="s">
+        <v>207</v>
+      </c>
+      <c r="H39" t="s">
+        <v>175</v>
+      </c>
+      <c r="J39" t="s">
+        <v>61</v>
+      </c>
+      <c r="K39" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>288</v>
+      </c>
+      <c r="B40" t="s">
+        <v>142</v>
+      </c>
+      <c r="C40" t="s">
+        <v>289</v>
+      </c>
+      <c r="D40" t="s">
+        <v>290</v>
+      </c>
+      <c r="E40" t="s">
+        <v>264</v>
+      </c>
+      <c r="F40" t="s">
+        <v>291</v>
+      </c>
+      <c r="G40" t="s">
+        <v>207</v>
+      </c>
+      <c r="H40" t="s">
+        <v>175</v>
+      </c>
+      <c r="J40" t="s">
+        <v>61</v>
+      </c>
+      <c r="K40" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>293</v>
+      </c>
+      <c r="B41" t="s">
+        <v>142</v>
+      </c>
+      <c r="C41" t="s">
+        <v>0</v>
+      </c>
+      <c r="D41" t="s">
+        <v>6</v>
+      </c>
+      <c r="E41" t="s">
+        <v>294</v>
+      </c>
+      <c r="F41" t="s">
+        <v>295</v>
+      </c>
+      <c r="G41" t="s">
+        <v>155</v>
+      </c>
+      <c r="H41" t="s">
+        <v>175</v>
+      </c>
+      <c r="J41" t="s">
+        <v>61</v>
+      </c>
+      <c r="K41" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>296</v>
+      </c>
+      <c r="B42" t="s">
+        <v>142</v>
+      </c>
+      <c r="C42" t="s">
+        <v>267</v>
+      </c>
+      <c r="D42" t="s">
+        <v>268</v>
+      </c>
+      <c r="E42" t="s">
+        <v>294</v>
+      </c>
+      <c r="F42" t="s">
+        <v>269</v>
+      </c>
+      <c r="G42" t="s">
+        <v>155</v>
+      </c>
+      <c r="H42" t="s">
+        <v>175</v>
+      </c>
+      <c r="J42" t="s">
+        <v>61</v>
+      </c>
+      <c r="K42" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>297</v>
+      </c>
+      <c r="B43" t="s">
+        <v>142</v>
+      </c>
+      <c r="C43" t="s">
+        <v>298</v>
+      </c>
+      <c r="D43" t="s">
+        <v>299</v>
+      </c>
+      <c r="E43" t="s">
+        <v>294</v>
+      </c>
+      <c r="F43" t="s">
+        <v>300</v>
+      </c>
+      <c r="H43" t="s">
+        <v>175</v>
+      </c>
+      <c r="J43" t="s">
+        <v>61</v>
+      </c>
+      <c r="K43" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>302</v>
+      </c>
+      <c r="B44" t="s">
+        <v>142</v>
+      </c>
+      <c r="C44" t="s">
+        <v>303</v>
+      </c>
+      <c r="D44" t="s">
+        <v>304</v>
+      </c>
+      <c r="E44" t="s">
+        <v>294</v>
+      </c>
+      <c r="F44" t="s">
+        <v>305</v>
+      </c>
+      <c r="G44" t="s">
+        <v>306</v>
+      </c>
+      <c r="H44" t="s">
+        <v>175</v>
+      </c>
+      <c r="J44" t="s">
+        <v>61</v>
+      </c>
+      <c r="K44" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>308</v>
+      </c>
+      <c r="B45" t="s">
+        <v>142</v>
+      </c>
+      <c r="C45" t="s">
+        <v>309</v>
+      </c>
+      <c r="D45" t="s">
+        <v>310</v>
+      </c>
+      <c r="E45" t="s">
+        <v>294</v>
+      </c>
+      <c r="F45" t="s">
+        <v>311</v>
+      </c>
+      <c r="G45" t="s">
+        <v>312</v>
+      </c>
+      <c r="H45" t="s">
+        <v>175</v>
+      </c>
+      <c r="J45" t="s">
+        <v>61</v>
+      </c>
+      <c r="K45" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>314</v>
+      </c>
+      <c r="B46" t="s">
+        <v>142</v>
+      </c>
+      <c r="C46" t="s">
+        <v>315</v>
+      </c>
+      <c r="D46" t="s">
+        <v>316</v>
+      </c>
+      <c r="E46" t="s">
+        <v>294</v>
+      </c>
+      <c r="F46" t="s">
+        <v>317</v>
+      </c>
+      <c r="G46" t="s">
+        <v>318</v>
+      </c>
+      <c r="H46" t="s">
+        <v>175</v>
+      </c>
+      <c r="J46" t="s">
+        <v>61</v>
+      </c>
+      <c r="K46" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>320</v>
+      </c>
+      <c r="B47" t="s">
+        <v>142</v>
+      </c>
+      <c r="C47" t="s">
+        <v>237</v>
+      </c>
+      <c r="D47" t="s">
+        <v>51</v>
+      </c>
+      <c r="E47" t="s">
+        <v>321</v>
+      </c>
+      <c r="F47" t="s">
+        <v>322</v>
+      </c>
+      <c r="G47" t="s">
+        <v>323</v>
+      </c>
+      <c r="H47" t="s">
+        <v>175</v>
+      </c>
+      <c r="J47" t="s">
+        <v>61</v>
+      </c>
+      <c r="K47" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>324</v>
+      </c>
+      <c r="B48" t="s">
+        <v>142</v>
+      </c>
+      <c r="C48" t="s">
+        <v>0</v>
+      </c>
+      <c r="D48" t="s">
+        <v>6</v>
+      </c>
+      <c r="E48" t="s">
+        <v>213</v>
+      </c>
+      <c r="F48" t="s">
+        <v>325</v>
+      </c>
+      <c r="G48" t="s">
+        <v>155</v>
+      </c>
+      <c r="H48" t="s">
+        <v>175</v>
+      </c>
+      <c r="J48" t="s">
+        <v>61</v>
+      </c>
+      <c r="K48" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>326</v>
+      </c>
+      <c r="B49" t="s">
+        <v>142</v>
+      </c>
+      <c r="C49" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>208</v>
-      </c>
-      <c r="B30" t="s">
-        <v>111</v>
-      </c>
-      <c r="C30" t="s">
-        <v>209</v>
-      </c>
-      <c r="D30" t="s">
-        <v>209</v>
-      </c>
-      <c r="E30" t="s">
-        <v>210</v>
-      </c>
-      <c r="F30" t="s">
-        <v>206</v>
-      </c>
-      <c r="G30" t="s">
-        <v>211</v>
-      </c>
-      <c r="H30" t="s">
-        <v>115</v>
-      </c>
-      <c r="I30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>212</v>
-      </c>
-      <c r="B31" t="s">
-        <v>111</v>
-      </c>
-      <c r="C31" t="s">
-        <v>160</v>
-      </c>
-      <c r="D31" t="s">
-        <v>160</v>
-      </c>
-      <c r="E31" t="s">
-        <v>161</v>
-      </c>
-      <c r="F31" t="s">
-        <v>206</v>
-      </c>
-      <c r="G31" t="s">
+      <c r="D49" t="s">
+        <v>327</v>
+      </c>
+      <c r="E49" t="s">
         <v>213</v>
       </c>
-      <c r="H31" t="s">
-        <v>163</v>
-      </c>
-      <c r="I31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>214</v>
-      </c>
-      <c r="B32" t="s">
-        <v>111</v>
-      </c>
-      <c r="C32" t="s">
-        <v>215</v>
-      </c>
-      <c r="D32" t="s">
-        <v>215</v>
-      </c>
-      <c r="E32" t="s">
-        <v>216</v>
-      </c>
-      <c r="F32" t="s">
-        <v>206</v>
-      </c>
-      <c r="G32" t="s">
-        <v>217</v>
-      </c>
-      <c r="H32" t="s">
-        <v>153</v>
-      </c>
-      <c r="I32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>218</v>
-      </c>
-      <c r="B33" t="s">
-        <v>111</v>
-      </c>
-      <c r="C33" t="s">
-        <v>219</v>
-      </c>
-      <c r="D33" t="s">
-        <v>219</v>
-      </c>
-      <c r="E33" t="s">
-        <v>220</v>
-      </c>
-      <c r="F33" t="s">
-        <v>206</v>
-      </c>
-      <c r="G33" t="s">
-        <v>221</v>
-      </c>
-      <c r="H33" t="s">
-        <v>153</v>
-      </c>
-      <c r="I33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>222</v>
-      </c>
-      <c r="B34" t="s">
-        <v>111</v>
-      </c>
-      <c r="C34" t="s">
-        <v>223</v>
-      </c>
-      <c r="D34" t="s">
-        <v>223</v>
-      </c>
-      <c r="E34" t="s">
-        <v>224</v>
-      </c>
-      <c r="F34" t="s">
-        <v>206</v>
-      </c>
-      <c r="G34" t="s">
-        <v>225</v>
-      </c>
-      <c r="H34" t="s">
-        <v>153</v>
-      </c>
-      <c r="I34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>226</v>
-      </c>
-      <c r="B35" t="s">
-        <v>111</v>
-      </c>
-      <c r="C35" t="s">
-        <v>227</v>
-      </c>
-      <c r="D35" t="s">
-        <v>227</v>
-      </c>
-      <c r="E35" t="s">
-        <v>228</v>
-      </c>
-      <c r="F35" t="s">
-        <v>206</v>
-      </c>
-      <c r="G35" t="s">
-        <v>229</v>
-      </c>
-      <c r="H35" t="s">
-        <v>153</v>
-      </c>
-      <c r="I35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>230</v>
-      </c>
-      <c r="B36" t="s">
-        <v>111</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="F49" t="s">
+        <v>328</v>
+      </c>
+      <c r="G49" t="s">
+        <v>155</v>
+      </c>
+      <c r="H49" t="s">
+        <v>175</v>
+      </c>
+      <c r="J49" t="s">
+        <v>61</v>
+      </c>
+      <c r="K49" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>330</v>
+      </c>
+      <c r="B50" t="s">
+        <v>142</v>
+      </c>
+      <c r="C50" t="s">
+        <v>0</v>
+      </c>
+      <c r="D50" t="s">
         <v>6</v>
       </c>
-      <c r="D36" t="s">
-        <v>6</v>
-      </c>
-      <c r="E36" t="s">
-        <v>112</v>
-      </c>
-      <c r="F36" t="s">
-        <v>231</v>
-      </c>
-      <c r="G36" t="s">
-        <v>232</v>
-      </c>
-      <c r="H36" t="s">
-        <v>115</v>
-      </c>
-      <c r="I36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>233</v>
-      </c>
-      <c r="B37" t="s">
-        <v>111</v>
-      </c>
-      <c r="C37" t="s">
-        <v>209</v>
-      </c>
-      <c r="D37" t="s">
-        <v>209</v>
-      </c>
-      <c r="E37" t="s">
-        <v>210</v>
-      </c>
-      <c r="F37" t="s">
-        <v>231</v>
-      </c>
-      <c r="G37" t="s">
-        <v>211</v>
-      </c>
-      <c r="H37" t="s">
-        <v>115</v>
-      </c>
-      <c r="I37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>234</v>
-      </c>
-      <c r="B38" t="s">
-        <v>111</v>
-      </c>
-      <c r="C38" t="s">
-        <v>235</v>
-      </c>
-      <c r="D38" t="s">
-        <v>235</v>
-      </c>
-      <c r="E38" t="s">
-        <v>236</v>
-      </c>
-      <c r="F38" t="s">
-        <v>231</v>
-      </c>
-      <c r="G38" t="s">
-        <v>237</v>
-      </c>
-      <c r="I38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>238</v>
-      </c>
-      <c r="B39" t="s">
-        <v>111</v>
-      </c>
-      <c r="C39" t="s">
-        <v>239</v>
-      </c>
-      <c r="D39" t="s">
-        <v>239</v>
-      </c>
-      <c r="E39" t="s">
-        <v>240</v>
-      </c>
-      <c r="F39" t="s">
-        <v>231</v>
-      </c>
-      <c r="G39" t="s">
-        <v>241</v>
-      </c>
-      <c r="H39" t="s">
-        <v>242</v>
-      </c>
-      <c r="I39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>243</v>
-      </c>
-      <c r="B40" t="s">
-        <v>111</v>
-      </c>
-      <c r="C40" t="s">
-        <v>244</v>
-      </c>
-      <c r="D40" t="s">
-        <v>244</v>
-      </c>
-      <c r="E40" t="s">
-        <v>245</v>
-      </c>
-      <c r="F40" t="s">
-        <v>231</v>
-      </c>
-      <c r="G40" t="s">
-        <v>246</v>
-      </c>
-      <c r="H40" t="s">
-        <v>247</v>
-      </c>
-      <c r="I40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>248</v>
-      </c>
-      <c r="B41" t="s">
-        <v>111</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="E50" t="s">
+        <v>171</v>
+      </c>
+      <c r="F50" t="s">
+        <v>331</v>
+      </c>
+      <c r="G50" t="s">
+        <v>155</v>
+      </c>
+      <c r="H50" t="s">
+        <v>175</v>
+      </c>
+      <c r="J50" t="s">
+        <v>61</v>
+      </c>
+      <c r="K50" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>332</v>
+      </c>
+      <c r="B51" t="s">
+        <v>142</v>
+      </c>
+      <c r="C51" t="s">
+        <v>147</v>
+      </c>
+      <c r="D51" t="s">
+        <v>148</v>
+      </c>
+      <c r="E51" t="s">
+        <v>171</v>
+      </c>
+      <c r="F51" t="s">
+        <v>333</v>
+      </c>
+      <c r="J51" t="s">
+        <v>61</v>
+      </c>
+      <c r="K51" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>334</v>
+      </c>
+      <c r="B52" t="s">
+        <v>142</v>
+      </c>
+      <c r="C52" t="s">
+        <v>335</v>
+      </c>
+      <c r="D52" t="s">
+        <v>336</v>
+      </c>
+      <c r="E52" t="s">
+        <v>171</v>
+      </c>
+      <c r="F52" t="s">
+        <v>337</v>
+      </c>
+      <c r="G52" t="s">
+        <v>155</v>
+      </c>
+      <c r="H52" t="s">
+        <v>175</v>
+      </c>
+      <c r="J52" t="s">
+        <v>61</v>
+      </c>
+      <c r="K52" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>339</v>
+      </c>
+      <c r="B53" t="s">
+        <v>142</v>
+      </c>
+      <c r="C53" t="s">
+        <v>340</v>
+      </c>
+      <c r="D53" t="s">
+        <v>341</v>
+      </c>
+      <c r="E53" t="s">
+        <v>171</v>
+      </c>
+      <c r="F53" t="s">
+        <v>342</v>
+      </c>
+      <c r="G53" t="s">
+        <v>155</v>
+      </c>
+      <c r="J53" t="s">
+        <v>61</v>
+      </c>
+      <c r="K53" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>344</v>
+      </c>
+      <c r="B54" t="s">
+        <v>142</v>
+      </c>
+      <c r="C54" t="s">
+        <v>345</v>
+      </c>
+      <c r="D54" t="s">
+        <v>346</v>
+      </c>
+      <c r="E54" t="s">
+        <v>171</v>
+      </c>
+      <c r="F54" t="s">
+        <v>347</v>
+      </c>
+      <c r="G54" t="s">
+        <v>207</v>
+      </c>
+      <c r="H54" t="s">
+        <v>175</v>
+      </c>
+      <c r="J54" t="s">
+        <v>61</v>
+      </c>
+      <c r="K54" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>349</v>
+      </c>
+      <c r="B55" t="s">
+        <v>142</v>
+      </c>
+      <c r="C55" t="s">
+        <v>350</v>
+      </c>
+      <c r="D55" t="s">
+        <v>351</v>
+      </c>
+      <c r="E55" t="s">
+        <v>171</v>
+      </c>
+      <c r="F55" t="s">
+        <v>352</v>
+      </c>
+      <c r="G55" t="s">
+        <v>155</v>
+      </c>
+      <c r="H55" t="s">
+        <v>175</v>
+      </c>
+      <c r="J55" t="s">
+        <v>61</v>
+      </c>
+      <c r="K55" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>354</v>
+      </c>
+      <c r="B56" t="s">
+        <v>142</v>
+      </c>
+      <c r="C56" t="s">
+        <v>355</v>
+      </c>
+      <c r="D56" t="s">
+        <v>356</v>
+      </c>
+      <c r="E56" t="s">
+        <v>171</v>
+      </c>
+      <c r="F56" t="s">
+        <v>357</v>
+      </c>
+      <c r="G56" t="s">
+        <v>155</v>
+      </c>
+      <c r="H56" t="s">
+        <v>175</v>
+      </c>
+      <c r="J56" t="s">
+        <v>61</v>
+      </c>
+      <c r="K56" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>359</v>
+      </c>
+      <c r="B57" t="s">
+        <v>142</v>
+      </c>
+      <c r="C57" t="s">
+        <v>184</v>
+      </c>
+      <c r="D57" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" t="s">
         <v>249</v>
       </c>
-      <c r="D41" t="s">
+      <c r="F57" t="s">
+        <v>360</v>
+      </c>
+      <c r="G57" t="s">
+        <v>155</v>
+      </c>
+      <c r="I57" t="s">
+        <v>175</v>
+      </c>
+      <c r="J57" t="s">
+        <v>61</v>
+      </c>
+      <c r="K57" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>361</v>
+      </c>
+      <c r="B58" t="s">
+        <v>142</v>
+      </c>
+      <c r="C58" t="s">
+        <v>362</v>
+      </c>
+      <c r="D58" t="s">
+        <v>363</v>
+      </c>
+      <c r="E58" t="s">
         <v>249</v>
       </c>
-      <c r="E41" t="s">
-        <v>250</v>
-      </c>
-      <c r="F41" t="s">
-        <v>231</v>
-      </c>
-      <c r="G41" t="s">
-        <v>251</v>
-      </c>
-      <c r="H41" t="s">
-        <v>252</v>
-      </c>
-      <c r="I41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>253</v>
-      </c>
-      <c r="B42" t="s">
-        <v>111</v>
-      </c>
-      <c r="C42" t="s">
-        <v>48</v>
-      </c>
-      <c r="D42" t="s">
-        <v>48</v>
-      </c>
-      <c r="E42" t="s">
-        <v>181</v>
-      </c>
-      <c r="F42" t="s">
-        <v>242</v>
-      </c>
-      <c r="G42" t="s">
-        <v>254</v>
-      </c>
-      <c r="H42" t="s">
-        <v>195</v>
-      </c>
-      <c r="I42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>255</v>
-      </c>
-      <c r="B43" t="s">
-        <v>111</v>
-      </c>
-      <c r="C43" t="s">
-        <v>6</v>
-      </c>
-      <c r="D43" t="s">
-        <v>6</v>
-      </c>
-      <c r="E43" t="s">
-        <v>112</v>
-      </c>
-      <c r="F43" t="s">
-        <v>158</v>
-      </c>
-      <c r="G43" t="s">
-        <v>256</v>
-      </c>
-      <c r="H43" t="s">
-        <v>115</v>
-      </c>
-      <c r="I43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>257</v>
-      </c>
-      <c r="B44" t="s">
-        <v>111</v>
-      </c>
-      <c r="C44" t="s">
-        <v>258</v>
-      </c>
-      <c r="D44" t="s">
-        <v>258</v>
-      </c>
-      <c r="E44" t="s">
-        <v>259</v>
-      </c>
-      <c r="F44" t="s">
-        <v>158</v>
-      </c>
-      <c r="G44" t="s">
-        <v>260</v>
-      </c>
-      <c r="H44" t="s">
-        <v>115</v>
-      </c>
-      <c r="I44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>261</v>
-      </c>
-      <c r="B45" t="s">
-        <v>111</v>
-      </c>
-      <c r="C45" t="s">
-        <v>6</v>
-      </c>
-      <c r="D45" t="s">
-        <v>6</v>
-      </c>
-      <c r="E45" t="s">
-        <v>112</v>
-      </c>
-      <c r="F45" t="s">
-        <v>262</v>
-      </c>
-      <c r="G45" t="s">
-        <v>263</v>
-      </c>
-      <c r="H45" t="s">
-        <v>115</v>
-      </c>
-      <c r="I45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="F58" t="s">
+        <v>364</v>
+      </c>
+      <c r="G58" t="s">
+        <v>191</v>
+      </c>
+      <c r="I58" t="s">
+        <v>175</v>
+      </c>
+      <c r="J58" t="s">
+        <v>61</v>
+      </c>
+      <c r="K58" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>366</v>
+      </c>
+      <c r="B59" t="s">
+        <v>142</v>
+      </c>
+      <c r="C59" t="s">
+        <v>367</v>
+      </c>
+      <c r="D59" t="s">
+        <v>368</v>
+      </c>
+      <c r="E59" t="s">
         <v>264</v>
       </c>
-      <c r="B46" t="s">
-        <v>111</v>
-      </c>
-      <c r="C46" t="s">
-        <v>160</v>
-      </c>
-      <c r="D46" t="s">
-        <v>160</v>
-      </c>
-      <c r="E46" t="s">
-        <v>161</v>
-      </c>
-      <c r="F46" t="s">
-        <v>262</v>
-      </c>
-      <c r="G46" t="s">
-        <v>265</v>
-      </c>
-      <c r="H46" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>266</v>
-      </c>
-      <c r="B47" t="s">
-        <v>111</v>
-      </c>
-      <c r="C47" t="s">
-        <v>267</v>
-      </c>
-      <c r="D47" t="s">
-        <v>267</v>
-      </c>
-      <c r="E47" t="s">
-        <v>268</v>
-      </c>
-      <c r="F47" t="s">
-        <v>262</v>
-      </c>
-      <c r="G47" t="s">
-        <v>269</v>
-      </c>
-      <c r="H47" t="s">
-        <v>115</v>
-      </c>
-      <c r="I47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>270</v>
-      </c>
-      <c r="B48" t="s">
-        <v>111</v>
-      </c>
-      <c r="C48" t="s">
-        <v>271</v>
-      </c>
-      <c r="D48" t="s">
-        <v>271</v>
-      </c>
-      <c r="E48" t="s">
-        <v>272</v>
-      </c>
-      <c r="F48" t="s">
-        <v>262</v>
-      </c>
-      <c r="G48" t="s">
-        <v>273</v>
-      </c>
-      <c r="H48" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>274</v>
-      </c>
-      <c r="B49" t="s">
-        <v>111</v>
-      </c>
-      <c r="C49" t="s">
-        <v>275</v>
-      </c>
-      <c r="D49" t="s">
-        <v>275</v>
-      </c>
-      <c r="E49" t="s">
-        <v>276</v>
-      </c>
-      <c r="F49" t="s">
-        <v>262</v>
-      </c>
-      <c r="G49" t="s">
-        <v>277</v>
-      </c>
-      <c r="H49" t="s">
-        <v>153</v>
-      </c>
-      <c r="I49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>278</v>
-      </c>
-      <c r="B50" t="s">
-        <v>111</v>
-      </c>
-      <c r="C50" t="s">
-        <v>279</v>
-      </c>
-      <c r="D50" t="s">
-        <v>279</v>
-      </c>
-      <c r="E50" t="s">
-        <v>280</v>
-      </c>
-      <c r="F50" t="s">
-        <v>262</v>
-      </c>
-      <c r="G50" t="s">
-        <v>281</v>
-      </c>
-      <c r="H50" t="s">
-        <v>115</v>
-      </c>
-      <c r="I50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>282</v>
-      </c>
-      <c r="B51" t="s">
-        <v>111</v>
-      </c>
-      <c r="C51" t="s">
-        <v>283</v>
-      </c>
-      <c r="D51" t="s">
-        <v>283</v>
-      </c>
-      <c r="E51" t="s">
-        <v>284</v>
-      </c>
-      <c r="F51" t="s">
-        <v>262</v>
-      </c>
-      <c r="G51" t="s">
-        <v>285</v>
-      </c>
-      <c r="H51" t="s">
-        <v>115</v>
-      </c>
-      <c r="I51">
-        <v>1</v>
+      <c r="F59" t="s">
+        <v>369</v>
+      </c>
+      <c r="G59" t="s">
+        <v>155</v>
+      </c>
+      <c r="I59" t="s">
+        <v>175</v>
+      </c>
+      <c r="J59" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>370</v>
+      </c>
+      <c r="B60" t="s">
+        <v>142</v>
+      </c>
+      <c r="C60" t="s">
+        <v>371</v>
+      </c>
+      <c r="D60" t="s">
+        <v>372</v>
+      </c>
+      <c r="E60" t="s">
+        <v>373</v>
+      </c>
+      <c r="F60" t="s">
+        <v>374</v>
+      </c>
+      <c r="G60" t="s">
+        <v>249</v>
+      </c>
+      <c r="H60" t="s">
+        <v>375</v>
+      </c>
+      <c r="J60" t="s">
+        <v>61</v>
+      </c>
+      <c r="K60" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>377</v>
+      </c>
+      <c r="B61" t="s">
+        <v>142</v>
+      </c>
+      <c r="C61" t="s">
+        <v>378</v>
+      </c>
+      <c r="D61" t="s">
+        <v>379</v>
+      </c>
+      <c r="E61" t="s">
+        <v>380</v>
+      </c>
+      <c r="F61" t="s">
+        <v>381</v>
+      </c>
+      <c r="G61" t="s">
+        <v>249</v>
+      </c>
+      <c r="H61" t="s">
+        <v>175</v>
+      </c>
+      <c r="I61" t="s">
+        <v>175</v>
+      </c>
+      <c r="J61" t="s">
+        <v>61</v>
+      </c>
+      <c r="K61" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>383</v>
+      </c>
+      <c r="B62" t="s">
+        <v>142</v>
+      </c>
+      <c r="C62" t="s">
+        <v>384</v>
+      </c>
+      <c r="D62" t="s">
+        <v>385</v>
+      </c>
+      <c r="E62" t="s">
+        <v>380</v>
+      </c>
+      <c r="F62" t="s">
+        <v>386</v>
+      </c>
+      <c r="G62" t="s">
+        <v>249</v>
+      </c>
+      <c r="H62" t="s">
+        <v>175</v>
+      </c>
+      <c r="I62" t="s">
+        <v>175</v>
+      </c>
+      <c r="J62" t="s">
+        <v>61</v>
+      </c>
+      <c r="K62" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>388</v>
+      </c>
+      <c r="B63" t="s">
+        <v>142</v>
+      </c>
+      <c r="C63" t="s">
+        <v>389</v>
+      </c>
+      <c r="D63" t="s">
+        <v>390</v>
+      </c>
+      <c r="E63" t="s">
+        <v>373</v>
+      </c>
+      <c r="F63" t="s">
+        <v>391</v>
+      </c>
+      <c r="G63" t="s">
+        <v>191</v>
+      </c>
+      <c r="I63" t="s">
+        <v>175</v>
+      </c>
+      <c r="J63" t="s">
+        <v>61</v>
+      </c>
+      <c r="K63" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>393</v>
+      </c>
+      <c r="B64" t="s">
+        <v>142</v>
+      </c>
+      <c r="C64" t="s">
+        <v>394</v>
+      </c>
+      <c r="D64" t="s">
+        <v>395</v>
+      </c>
+      <c r="E64" t="s">
+        <v>373</v>
+      </c>
+      <c r="F64" t="s">
+        <v>396</v>
+      </c>
+      <c r="G64" t="s">
+        <v>191</v>
+      </c>
+      <c r="I64" t="s">
+        <v>175</v>
+      </c>
+      <c r="J64" t="s">
+        <v>61</v>
+      </c>
+      <c r="K64" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>398</v>
+      </c>
+      <c r="B65" t="s">
+        <v>142</v>
+      </c>
+      <c r="C65" t="s">
+        <v>389</v>
+      </c>
+      <c r="D65" t="s">
+        <v>390</v>
+      </c>
+      <c r="E65" t="s">
+        <v>380</v>
+      </c>
+      <c r="F65" t="s">
+        <v>391</v>
+      </c>
+      <c r="G65" t="s">
+        <v>191</v>
+      </c>
+      <c r="I65" t="s">
+        <v>175</v>
+      </c>
+      <c r="J65" t="s">
+        <v>61</v>
+      </c>
+      <c r="K65" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>399</v>
+      </c>
+      <c r="B66" t="s">
+        <v>142</v>
+      </c>
+      <c r="C66" t="s">
+        <v>394</v>
+      </c>
+      <c r="D66" t="s">
+        <v>395</v>
+      </c>
+      <c r="E66" t="s">
+        <v>380</v>
+      </c>
+      <c r="F66" t="s">
+        <v>396</v>
+      </c>
+      <c r="G66" t="s">
+        <v>191</v>
+      </c>
+      <c r="I66" t="s">
+        <v>175</v>
+      </c>
+      <c r="J66" t="s">
+        <v>61</v>
+      </c>
+      <c r="K66" t="s">
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -3398,13 +4720,13 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="5" width="20" customWidth="1"/>
+    <col min="1" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -3418,24 +4740,42 @@
         <v>8</v>
       </c>
       <c r="E1" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+      <c r="F1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>287</v>
+        <v>400</v>
       </c>
       <c r="B2" t="s">
-        <v>288</v>
+        <v>121</v>
       </c>
       <c r="C2" t="s">
-        <v>289</v>
+        <v>401</v>
       </c>
       <c r="D2" t="s">
-        <v>290</v>
+        <v>402</v>
       </c>
       <c r="E2" t="s">
-        <v>291</v>
+        <v>403</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/profiles/rocphotos/profile-crate/ro-crate-metadata.xlsx
+++ b/profiles/rocphotos/profile-crate/ro-crate-metadata.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="413">
   <si>
     <t>Name</t>
   </si>
@@ -206,6 +206,9 @@
     <t>The entity that identifies the crate and points at its root data entity.</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>"#hasSpecializedSchema"</t>
   </si>
   <si>
@@ -221,7 +224,7 @@
     <t>"http://schema.org/Dataset"</t>
   </si>
   <si>
-    <t>The root of the main collection crate. Told apart from the other two roots by what its hasPart holds: the sub-collection folders, and any albums.</t>
+    <t>The root dataset of a rocphotos Main Collection, which includes references to all the "folder collections". This has the metadata for the Main Collection, which also includes detailed context such as relationships between people.</t>
   </si>
   <si>
     <t>#class_FolderCollectionRoot</t>
@@ -230,7 +233,7 @@
     <t>Folder collection root</t>
   </si>
   <si>
-    <t>The root of a crate for one folder of photos. Told apart from the other two roots by its hasPart holding photos.</t>
+    <t>The root dataset of a Folder Collection - describing all the images in a directory and its sub-directories.</t>
   </si>
   <si>
     <t>#class_FacesRoot</t>
@@ -239,7 +242,7 @@
     <t>Faces crate root</t>
   </si>
   <si>
-    <t>The root of the faces crate. Told apart from the other two roots by its hasPart holding face embeddings.</t>
+    <t>This is used by the rocphotos app for managing face data - it is not designed to be edited by people.</t>
   </si>
   <si>
     <t>#class_SubCollection</t>
@@ -248,7 +251,7 @@
     <t>Sub-collection reference</t>
   </si>
   <si>
-    <t>How the main collection root lists a sub-collection folder: a Dataset with a name and no hasPart of its own (its own crate holds the photos).</t>
+    <t>A reference to a Folder Collection from the Main Collection, just a pointer to where it is on disk. This is not intended to be edited by hand.</t>
   </si>
   <si>
     <t>#class_Photo</t>
@@ -263,7 +266,7 @@
     <t>"http://schema.org/ImageObject"</t>
   </si>
   <si>
-    <t>A source photograph. Distinguished from the crate's other ImageObjects (thumbnails, album items) by carrying a title, which is always present — the file's own IPTC/XMP title, or its filename.</t>
+    <t>A photograph. Distinguished from the crate's other ImageObjects (thumbnails, album items).</t>
   </si>
   <si>
     <t>#class_Thumbnail</t>
@@ -281,7 +284,7 @@
     <t>Album item</t>
   </si>
   <si>
-    <t>One photo's place in one album — a proxy, so a caption specific to this album could later hang off it without touching the shared photo.</t>
+    <t>A proxy reference to a photo in an album so a caption or other metadata specific to this album can later be added without changing the original picture.</t>
   </si>
   <si>
     <t>#class_Album</t>
@@ -296,7 +299,7 @@
     <t>"http://schema.org/ImageGallery"</t>
   </si>
   <si>
-    <t>A named, ordered virtual collection of photos, living in the root crate.</t>
+    <t>A named, ordered virtual collection of photos, which is stored in the Main Collection crate.</t>
   </si>
   <si>
     <t>#MainPersonClass</t>
@@ -308,7 +311,7 @@
     <t>"http://schema.org/Person"</t>
   </si>
   <si>
-    <t>A person, identified by name across the whole collection (arcp://name,rocphoto/person/&lt;NameSlug&gt;). The root crate's copy is the one to describe in full; each sub-collection crate carries a minimal copy so it reads standalone.</t>
+    <t>A person, identified by name across the whole collection using an id that is unique within the collections (eg arcp://name,rocphoto/person/&lt;NameSlug&gt;). The Main Crate has the 'canonical' or main description for each unique person represented in the collection.</t>
   </si>
   <si>
     <t>#InstancePersonClass</t>
@@ -413,7 +416,7 @@
     <t>#SpouseRelationshipClass</t>
   </si>
   <si>
-    <t>Married</t>
+    <t>Spouses</t>
   </si>
   <si>
     <t>rico:SpouseRelation</t>
@@ -422,7 +425,7 @@
     <t>"https://www.ica.org/standards/RiC/ontology#SpouseRelation"</t>
   </si>
   <si>
-    <t>Two people who are, or were, married to each other. Not oriented: it reads the same from either side. This is RiC's own SpouseRelation, used as it stands.</t>
+    <t>Relationship between people who are, or were, in a spousal relationship to each other, includes marriages, de-facto marriages and other long term partnerships.</t>
   </si>
   <si>
     <t>#ParentChildRelationshipClass</t>
@@ -437,7 +440,7 @@
     <t>"https://www.ica.org/standards/RiC/ontology#ChildRelation"</t>
   </si>
   <si>
-    <t>Oriented from the parent to the child: the parent is the source, the child is the target. This is RiC's own ChildRelation, used as it stands, including its direction — which runs down a generation rather than up.</t>
+    <t>A parent-child relationship including biological, adoptive or other forms.</t>
   </si>
   <si>
     <t>domainIncludes</t>
@@ -548,9 +551,6 @@
     <t>The sub-collection's path, e.g. 2025/03/10.</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>#prop_photo_name</t>
   </si>
   <si>
@@ -1134,9 +1134,6 @@
   </si>
   <si>
     <t>#prop_spouse_connects</t>
-  </si>
-  <si>
-    <t>Spouses</t>
   </si>
   <si>
     <t>rico:relationConnects</t>
@@ -1770,7 +1767,7 @@
         <v>8</v>
       </c>
       <c r="E1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F1" t="s">
         <v>28</v>
@@ -1778,22 +1775,22 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B2" t="s">
         <v>405</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>406</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>407</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>408</v>
       </c>
-      <c r="E2" t="s">
-        <v>409</v>
-      </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1826,16 +1823,16 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B2" t="s">
         <v>410</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>411</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>412</v>
-      </c>
-      <c r="D2" t="s">
-        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -2130,499 +2127,508 @@
       <c r="F2" t="s">
         <v>60</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
+      <c r="G2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2" t="s">
+        <v>61</v>
       </c>
       <c r="I2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="J3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="J4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I5" t="s">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="J5" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B7" t="s">
         <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B8" t="s">
         <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
         <v>56</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B10" t="s">
         <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B11" t="s">
         <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B12" t="s">
         <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B13" t="s">
         <v>56</v>
       </c>
       <c r="C13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B14" t="s">
         <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B15" t="s">
         <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B16" t="s">
         <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D16" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B17" t="s">
         <v>56</v>
       </c>
       <c r="C17" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F17" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J17" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B18" t="s">
         <v>56</v>
       </c>
       <c r="C18" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D18" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E18" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F18" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J18" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B19" t="s">
         <v>56</v>
       </c>
       <c r="C19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B20" t="s">
         <v>56</v>
       </c>
       <c r="C20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D20" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E20" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F20" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J20" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B21" t="s">
         <v>56</v>
       </c>
       <c r="C21" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E21" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2653,13 +2659,13 @@
         <v>50</v>
       </c>
       <c r="E1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F1" t="s">
         <v>52</v>
       </c>
       <c r="G1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H1" t="s">
         <v>53</v>
@@ -2676,10 +2682,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C2" t="s">
         <v>2</v>
@@ -2688,65 +2694,65 @@
         <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
+        <v>146</v>
+      </c>
+      <c r="H2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I2" t="s">
+        <v>61</v>
       </c>
       <c r="J2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G3" t="s">
-        <v>150</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
+        <v>151</v>
+      </c>
+      <c r="H3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I3" t="s">
+        <v>61</v>
       </c>
       <c r="J3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C4" t="s">
         <v>0</v>
@@ -2755,62 +2761,62 @@
         <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G4" t="s">
-        <v>155</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
+        <v>156</v>
+      </c>
+      <c r="H4" t="s">
+        <v>61</v>
       </c>
       <c r="J4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D5" t="s">
         <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
+        <v>161</v>
+      </c>
+      <c r="H5" t="s">
+        <v>61</v>
       </c>
       <c r="J5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C6" t="s">
         <v>0</v>
@@ -2819,62 +2825,62 @@
         <v>6</v>
       </c>
       <c r="E6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G6" t="s">
-        <v>155</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
+        <v>156</v>
+      </c>
+      <c r="H6" t="s">
+        <v>61</v>
       </c>
       <c r="J6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D7" t="s">
         <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G7" t="s">
-        <v>166</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
+        <v>167</v>
+      </c>
+      <c r="H7" t="s">
+        <v>61</v>
       </c>
       <c r="J7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C8" t="s">
         <v>0</v>
@@ -2883,62 +2889,62 @@
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G8" t="s">
-        <v>155</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
+        <v>156</v>
+      </c>
+      <c r="H8" t="s">
+        <v>61</v>
       </c>
       <c r="J8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D9" t="s">
         <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G9" t="s">
-        <v>171</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
+        <v>172</v>
+      </c>
+      <c r="H9" t="s">
+        <v>61</v>
       </c>
       <c r="J9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C10" t="s">
         <v>0</v>
@@ -2947,22 +2953,22 @@
         <v>6</v>
       </c>
       <c r="E10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H10" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -2970,7 +2976,7 @@
         <v>176</v>
       </c>
       <c r="B11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C11" t="s">
         <v>0</v>
@@ -2979,22 +2985,22 @@
         <v>6</v>
       </c>
       <c r="E11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F11" t="s">
         <v>177</v>
       </c>
       <c r="G11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H11" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -3002,7 +3008,7 @@
         <v>178</v>
       </c>
       <c r="B12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C12" t="s">
         <v>179</v>
@@ -3011,19 +3017,19 @@
         <v>180</v>
       </c>
       <c r="E12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F12" t="s">
         <v>181</v>
       </c>
       <c r="G12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H12" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K12" t="s">
         <v>182</v>
@@ -3034,7 +3040,7 @@
         <v>183</v>
       </c>
       <c r="B13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C13" t="s">
         <v>184</v>
@@ -3043,16 +3049,16 @@
         <v>8</v>
       </c>
       <c r="E13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F13" t="s">
         <v>185</v>
       </c>
       <c r="G13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K13" t="s">
         <v>186</v>
@@ -3063,7 +3069,7 @@
         <v>187</v>
       </c>
       <c r="B14" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C14" t="s">
         <v>188</v>
@@ -3072,7 +3078,7 @@
         <v>189</v>
       </c>
       <c r="E14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F14" t="s">
         <v>190</v>
@@ -3081,7 +3087,7 @@
         <v>191</v>
       </c>
       <c r="J14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K14" t="s">
         <v>192</v>
@@ -3092,7 +3098,7 @@
         <v>193</v>
       </c>
       <c r="B15" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C15" t="s">
         <v>194</v>
@@ -3101,7 +3107,7 @@
         <v>195</v>
       </c>
       <c r="E15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F15" t="s">
         <v>196</v>
@@ -3110,7 +3116,7 @@
         <v>191</v>
       </c>
       <c r="J15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K15" t="s">
         <v>197</v>
@@ -3121,7 +3127,7 @@
         <v>198</v>
       </c>
       <c r="B16" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C16" t="s">
         <v>199</v>
@@ -3130,16 +3136,16 @@
         <v>200</v>
       </c>
       <c r="E16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F16" t="s">
         <v>201</v>
       </c>
       <c r="G16" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K16" t="s">
         <v>202</v>
@@ -3150,7 +3156,7 @@
         <v>203</v>
       </c>
       <c r="B17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C17" t="s">
         <v>204</v>
@@ -3159,7 +3165,7 @@
         <v>205</v>
       </c>
       <c r="E17" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F17" t="s">
         <v>206</v>
@@ -3168,7 +3174,7 @@
         <v>207</v>
       </c>
       <c r="J17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K17" t="s">
         <v>208</v>
@@ -3179,7 +3185,7 @@
         <v>209</v>
       </c>
       <c r="B18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C18" t="s">
         <v>210</v>
@@ -3188,7 +3194,7 @@
         <v>211</v>
       </c>
       <c r="E18" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F18" t="s">
         <v>212</v>
@@ -3197,7 +3203,7 @@
         <v>213</v>
       </c>
       <c r="J18" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K18" t="s">
         <v>214</v>
@@ -3208,16 +3214,16 @@
         <v>215</v>
       </c>
       <c r="B19" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F19" t="s">
         <v>216</v>
@@ -3226,10 +3232,10 @@
         <v>217</v>
       </c>
       <c r="J19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -3237,7 +3243,7 @@
         <v>218</v>
       </c>
       <c r="B20" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C20" t="s">
         <v>219</v>
@@ -3246,7 +3252,7 @@
         <v>220</v>
       </c>
       <c r="E20" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F20" t="s">
         <v>221</v>
@@ -3255,7 +3261,7 @@
         <v>222</v>
       </c>
       <c r="J20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K20" t="s">
         <v>223</v>
@@ -3266,16 +3272,16 @@
         <v>224</v>
       </c>
       <c r="B21" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D21" t="s">
         <v>225</v>
       </c>
       <c r="E21" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F21" t="s">
         <v>226</v>
@@ -3284,7 +3290,7 @@
         <v>227</v>
       </c>
       <c r="J21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K21" t="s">
         <v>228</v>
@@ -3295,7 +3301,7 @@
         <v>229</v>
       </c>
       <c r="B22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C22" t="s">
         <v>230</v>
@@ -3304,16 +3310,16 @@
         <v>231</v>
       </c>
       <c r="E22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F22" t="s">
         <v>232</v>
       </c>
       <c r="G22" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K22" t="s">
         <v>233</v>
@@ -3324,7 +3330,7 @@
         <v>234</v>
       </c>
       <c r="B23" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C23" t="s">
         <v>0</v>
@@ -3339,16 +3345,16 @@
         <v>235</v>
       </c>
       <c r="G23" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H23" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K23" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -3356,7 +3362,7 @@
         <v>236</v>
       </c>
       <c r="B24" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C24" t="s">
         <v>237</v>
@@ -3371,10 +3377,10 @@
         <v>239</v>
       </c>
       <c r="H24" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K24" t="s">
         <v>240</v>
@@ -3385,7 +3391,7 @@
         <v>241</v>
       </c>
       <c r="B25" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C25" t="s">
         <v>0</v>
@@ -3400,16 +3406,16 @@
         <v>243</v>
       </c>
       <c r="G25" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H25" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J25" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K25" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -3417,7 +3423,7 @@
         <v>244</v>
       </c>
       <c r="B26" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C26" t="s">
         <v>184</v>
@@ -3432,10 +3438,10 @@
         <v>245</v>
       </c>
       <c r="G26" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K26" t="s">
         <v>186</v>
@@ -3446,10 +3452,10 @@
         <v>246</v>
       </c>
       <c r="B27" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C27" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D27" t="s">
         <v>22</v>
@@ -3464,13 +3470,13 @@
         <v>238</v>
       </c>
       <c r="H27" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K27" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -3478,7 +3484,7 @@
         <v>248</v>
       </c>
       <c r="B28" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C28" t="s">
         <v>0</v>
@@ -3493,16 +3499,16 @@
         <v>250</v>
       </c>
       <c r="G28" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H28" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J28" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -3510,7 +3516,7 @@
         <v>251</v>
       </c>
       <c r="B29" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C29" t="s">
         <v>0</v>
@@ -3525,16 +3531,16 @@
         <v>253</v>
       </c>
       <c r="G29" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H29" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K29" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -3542,7 +3548,7 @@
         <v>254</v>
       </c>
       <c r="B30" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C30" t="s">
         <v>237</v>
@@ -3560,10 +3566,10 @@
         <v>249</v>
       </c>
       <c r="H30" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J30" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K30" t="s">
         <v>240</v>
@@ -3574,7 +3580,7 @@
         <v>256</v>
       </c>
       <c r="B31" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C31" t="s">
         <v>0</v>
@@ -3589,16 +3595,16 @@
         <v>258</v>
       </c>
       <c r="G31" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H31" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J31" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K31" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -3606,7 +3612,7 @@
         <v>259</v>
       </c>
       <c r="B32" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C32" t="s">
         <v>0</v>
@@ -3621,16 +3627,16 @@
         <v>261</v>
       </c>
       <c r="G32" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H32" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J32" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K32" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -3638,7 +3644,7 @@
         <v>262</v>
       </c>
       <c r="B33" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C33" t="s">
         <v>237</v>
@@ -3656,10 +3662,10 @@
         <v>257</v>
       </c>
       <c r="H33" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J33" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K33" t="s">
         <v>240</v>
@@ -3670,7 +3676,7 @@
         <v>263</v>
       </c>
       <c r="B34" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C34" t="s">
         <v>0</v>
@@ -3685,16 +3691,16 @@
         <v>265</v>
       </c>
       <c r="G34" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H34" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -3702,7 +3708,7 @@
         <v>266</v>
       </c>
       <c r="B35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C35" t="s">
         <v>267</v>
@@ -3717,13 +3723,13 @@
         <v>269</v>
       </c>
       <c r="G35" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H35" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K35" t="s">
         <v>270</v>
@@ -3734,13 +3740,13 @@
         <v>271</v>
       </c>
       <c r="B36" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C36" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D36" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E36" t="s">
         <v>264</v>
@@ -3752,13 +3758,13 @@
         <v>217</v>
       </c>
       <c r="H36" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J36" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K36" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -3766,7 +3772,7 @@
         <v>273</v>
       </c>
       <c r="B37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C37" t="s">
         <v>274</v>
@@ -3784,10 +3790,10 @@
         <v>207</v>
       </c>
       <c r="H37" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K37" t="s">
         <v>277</v>
@@ -3798,7 +3804,7 @@
         <v>278</v>
       </c>
       <c r="B38" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C38" t="s">
         <v>279</v>
@@ -3816,10 +3822,10 @@
         <v>207</v>
       </c>
       <c r="H38" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J38" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K38" t="s">
         <v>282</v>
@@ -3830,7 +3836,7 @@
         <v>283</v>
       </c>
       <c r="B39" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C39" t="s">
         <v>284</v>
@@ -3848,10 +3854,10 @@
         <v>207</v>
       </c>
       <c r="H39" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J39" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K39" t="s">
         <v>287</v>
@@ -3862,7 +3868,7 @@
         <v>288</v>
       </c>
       <c r="B40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C40" t="s">
         <v>289</v>
@@ -3880,10 +3886,10 @@
         <v>207</v>
       </c>
       <c r="H40" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J40" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K40" t="s">
         <v>292</v>
@@ -3894,7 +3900,7 @@
         <v>293</v>
       </c>
       <c r="B41" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C41" t="s">
         <v>0</v>
@@ -3909,16 +3915,16 @@
         <v>295</v>
       </c>
       <c r="G41" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H41" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K41" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -3926,7 +3932,7 @@
         <v>296</v>
       </c>
       <c r="B42" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C42" t="s">
         <v>267</v>
@@ -3941,13 +3947,13 @@
         <v>269</v>
       </c>
       <c r="G42" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H42" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J42" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K42" t="s">
         <v>270</v>
@@ -3958,7 +3964,7 @@
         <v>297</v>
       </c>
       <c r="B43" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C43" t="s">
         <v>298</v>
@@ -3973,10 +3979,10 @@
         <v>300</v>
       </c>
       <c r="H43" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J43" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K43" t="s">
         <v>301</v>
@@ -3987,7 +3993,7 @@
         <v>302</v>
       </c>
       <c r="B44" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C44" t="s">
         <v>303</v>
@@ -4005,10 +4011,10 @@
         <v>306</v>
       </c>
       <c r="H44" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J44" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K44" t="s">
         <v>307</v>
@@ -4019,7 +4025,7 @@
         <v>308</v>
       </c>
       <c r="B45" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C45" t="s">
         <v>309</v>
@@ -4037,10 +4043,10 @@
         <v>312</v>
       </c>
       <c r="H45" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J45" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K45" t="s">
         <v>313</v>
@@ -4051,7 +4057,7 @@
         <v>314</v>
       </c>
       <c r="B46" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C46" t="s">
         <v>315</v>
@@ -4069,10 +4075,10 @@
         <v>318</v>
       </c>
       <c r="H46" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J46" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K46" t="s">
         <v>319</v>
@@ -4083,7 +4089,7 @@
         <v>320</v>
       </c>
       <c r="B47" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C47" t="s">
         <v>237</v>
@@ -4101,10 +4107,10 @@
         <v>323</v>
       </c>
       <c r="H47" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J47" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K47" t="s">
         <v>240</v>
@@ -4115,7 +4121,7 @@
         <v>324</v>
       </c>
       <c r="B48" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C48" t="s">
         <v>0</v>
@@ -4130,16 +4136,16 @@
         <v>325</v>
       </c>
       <c r="G48" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H48" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J48" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K48" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -4147,7 +4153,7 @@
         <v>326</v>
       </c>
       <c r="B49" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C49" t="s">
         <v>1</v>
@@ -4162,13 +4168,13 @@
         <v>328</v>
       </c>
       <c r="G49" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H49" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J49" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K49" t="s">
         <v>329</v>
@@ -4179,7 +4185,7 @@
         <v>330</v>
       </c>
       <c r="B50" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C50" t="s">
         <v>0</v>
@@ -4188,22 +4194,22 @@
         <v>6</v>
       </c>
       <c r="E50" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F50" t="s">
         <v>331</v>
       </c>
       <c r="G50" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H50" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J50" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K50" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -4211,25 +4217,25 @@
         <v>332</v>
       </c>
       <c r="B51" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C51" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D51" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E51" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F51" t="s">
         <v>333</v>
       </c>
       <c r="J51" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K51" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -4237,7 +4243,7 @@
         <v>334</v>
       </c>
       <c r="B52" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C52" t="s">
         <v>335</v>
@@ -4246,19 +4252,19 @@
         <v>336</v>
       </c>
       <c r="E52" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F52" t="s">
         <v>337</v>
       </c>
       <c r="G52" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H52" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J52" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K52" t="s">
         <v>338</v>
@@ -4269,7 +4275,7 @@
         <v>339</v>
       </c>
       <c r="B53" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C53" t="s">
         <v>340</v>
@@ -4278,16 +4284,16 @@
         <v>341</v>
       </c>
       <c r="E53" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F53" t="s">
         <v>342</v>
       </c>
       <c r="G53" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J53" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K53" t="s">
         <v>343</v>
@@ -4298,7 +4304,7 @@
         <v>344</v>
       </c>
       <c r="B54" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C54" t="s">
         <v>345</v>
@@ -4307,7 +4313,7 @@
         <v>346</v>
       </c>
       <c r="E54" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F54" t="s">
         <v>347</v>
@@ -4316,10 +4322,10 @@
         <v>207</v>
       </c>
       <c r="H54" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J54" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K54" t="s">
         <v>348</v>
@@ -4330,7 +4336,7 @@
         <v>349</v>
       </c>
       <c r="B55" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C55" t="s">
         <v>350</v>
@@ -4339,19 +4345,19 @@
         <v>351</v>
       </c>
       <c r="E55" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F55" t="s">
         <v>352</v>
       </c>
       <c r="G55" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H55" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J55" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K55" t="s">
         <v>353</v>
@@ -4362,7 +4368,7 @@
         <v>354</v>
       </c>
       <c r="B56" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C56" t="s">
         <v>355</v>
@@ -4371,19 +4377,19 @@
         <v>356</v>
       </c>
       <c r="E56" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F56" t="s">
         <v>357</v>
       </c>
       <c r="G56" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H56" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J56" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K56" t="s">
         <v>358</v>
@@ -4394,7 +4400,7 @@
         <v>359</v>
       </c>
       <c r="B57" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C57" t="s">
         <v>184</v>
@@ -4409,13 +4415,13 @@
         <v>360</v>
       </c>
       <c r="G57" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I57" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J57" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K57" t="s">
         <v>186</v>
@@ -4426,7 +4432,7 @@
         <v>361</v>
       </c>
       <c r="B58" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C58" t="s">
         <v>362</v>
@@ -4444,10 +4450,10 @@
         <v>191</v>
       </c>
       <c r="I58" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J58" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K58" t="s">
         <v>365</v>
@@ -4458,7 +4464,7 @@
         <v>366</v>
       </c>
       <c r="B59" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C59" t="s">
         <v>367</v>
@@ -4473,13 +4479,13 @@
         <v>369</v>
       </c>
       <c r="G59" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I59" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J59" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -4487,229 +4493,229 @@
         <v>370</v>
       </c>
       <c r="B60" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C60" t="s">
+        <v>131</v>
+      </c>
+      <c r="D60" t="s">
         <v>371</v>
       </c>
-      <c r="D60" t="s">
+      <c r="E60" t="s">
         <v>372</v>
       </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
         <v>373</v>
-      </c>
-      <c r="F60" t="s">
-        <v>374</v>
       </c>
       <c r="G60" t="s">
         <v>249</v>
       </c>
       <c r="H60" t="s">
+        <v>374</v>
+      </c>
+      <c r="J60" t="s">
+        <v>62</v>
+      </c>
+      <c r="K60" t="s">
         <v>375</v>
-      </c>
-      <c r="J60" t="s">
-        <v>61</v>
-      </c>
-      <c r="K60" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>376</v>
+      </c>
+      <c r="B61" t="s">
+        <v>143</v>
+      </c>
+      <c r="C61" t="s">
         <v>377</v>
       </c>
-      <c r="B61" t="s">
-        <v>142</v>
-      </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
         <v>378</v>
       </c>
-      <c r="D61" t="s">
+      <c r="E61" t="s">
         <v>379</v>
       </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>380</v>
-      </c>
-      <c r="F61" t="s">
-        <v>381</v>
       </c>
       <c r="G61" t="s">
         <v>249</v>
       </c>
       <c r="H61" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="I61" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J61" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K61" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>382</v>
+      </c>
+      <c r="B62" t="s">
+        <v>143</v>
+      </c>
+      <c r="C62" t="s">
         <v>383</v>
       </c>
-      <c r="B62" t="s">
-        <v>142</v>
-      </c>
-      <c r="C62" t="s">
+      <c r="D62" t="s">
         <v>384</v>
       </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
+        <v>379</v>
+      </c>
+      <c r="F62" t="s">
         <v>385</v>
-      </c>
-      <c r="E62" t="s">
-        <v>380</v>
-      </c>
-      <c r="F62" t="s">
-        <v>386</v>
       </c>
       <c r="G62" t="s">
         <v>249</v>
       </c>
       <c r="H62" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="I62" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J62" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K62" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>387</v>
+      </c>
+      <c r="B63" t="s">
+        <v>143</v>
+      </c>
+      <c r="C63" t="s">
         <v>388</v>
       </c>
-      <c r="B63" t="s">
-        <v>142</v>
-      </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
         <v>389</v>
       </c>
-      <c r="D63" t="s">
+      <c r="E63" t="s">
+        <v>372</v>
+      </c>
+      <c r="F63" t="s">
         <v>390</v>
-      </c>
-      <c r="E63" t="s">
-        <v>373</v>
-      </c>
-      <c r="F63" t="s">
-        <v>391</v>
       </c>
       <c r="G63" t="s">
         <v>191</v>
       </c>
       <c r="I63" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J63" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K63" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>392</v>
+      </c>
+      <c r="B64" t="s">
+        <v>143</v>
+      </c>
+      <c r="C64" t="s">
         <v>393</v>
       </c>
-      <c r="B64" t="s">
-        <v>142</v>
-      </c>
-      <c r="C64" t="s">
+      <c r="D64" t="s">
         <v>394</v>
       </c>
-      <c r="D64" t="s">
+      <c r="E64" t="s">
+        <v>372</v>
+      </c>
+      <c r="F64" t="s">
         <v>395</v>
-      </c>
-      <c r="E64" t="s">
-        <v>373</v>
-      </c>
-      <c r="F64" t="s">
-        <v>396</v>
       </c>
       <c r="G64" t="s">
         <v>191</v>
       </c>
       <c r="I64" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J64" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K64" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B65" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C65" t="s">
+        <v>388</v>
+      </c>
+      <c r="D65" t="s">
         <v>389</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
+        <v>379</v>
+      </c>
+      <c r="F65" t="s">
         <v>390</v>
-      </c>
-      <c r="E65" t="s">
-        <v>380</v>
-      </c>
-      <c r="F65" t="s">
-        <v>391</v>
       </c>
       <c r="G65" t="s">
         <v>191</v>
       </c>
       <c r="I65" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J65" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K65" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B66" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C66" t="s">
+        <v>393</v>
+      </c>
+      <c r="D66" t="s">
         <v>394</v>
       </c>
-      <c r="D66" t="s">
+      <c r="E66" t="s">
+        <v>379</v>
+      </c>
+      <c r="F66" t="s">
         <v>395</v>
-      </c>
-      <c r="E66" t="s">
-        <v>380</v>
-      </c>
-      <c r="F66" t="s">
-        <v>396</v>
       </c>
       <c r="G66" t="s">
         <v>191</v>
       </c>
       <c r="I66" t="s">
-        <v>175</v>
+        <v>61</v>
       </c>
       <c r="J66" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K66" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -4754,28 +4760,28 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" t="s">
         <v>400</v>
       </c>
-      <c r="B2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>401</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>402</v>
       </c>
-      <c r="E2" t="s">
-        <v>403</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
+      <c r="F2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G2" t="s">
+        <v>61</v>
       </c>
       <c r="H2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
